--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/3_five_bus_radial_grid_1ph_dyn_MP_pf_sc_results_4_branch.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/3_five_bus_radial_grid_1ph_dyn_MP_pf_sc_results_4_branch.xlsx
@@ -646,10 +646,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.8010071194443309</v>
+        <v>0.8010071194438342</v>
       </c>
       <c r="C2">
-        <v>0.8010071194443309</v>
+        <v>0.8010071194438342</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -658,40 +658,40 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>27.74770056203947</v>
+        <v>27.74770056202226</v>
       </c>
       <c r="G2">
-        <v>27.74770056203947</v>
+        <v>27.74770056202226</v>
       </c>
       <c r="H2">
-        <v>3.34652257451091</v>
+        <v>3.346522574404258</v>
       </c>
       <c r="I2">
-        <v>-2.345607201434873</v>
+        <v>-2.345607201329441</v>
       </c>
       <c r="J2">
-        <v>24.47415207743945</v>
+        <v>24.47415207745156</v>
       </c>
       <c r="K2">
-        <v>-23.33849811299677</v>
+        <v>-23.33849811301025</v>
       </c>
       <c r="L2">
-        <v>67.00637072519021</v>
+        <v>-82.99362927492932</v>
       </c>
       <c r="M2">
-        <v>-112.9936292748025</v>
+        <v>97.00637072506339</v>
       </c>
       <c r="N2">
-        <v>0.8902319386642066</v>
+        <v>0.8902319386646702</v>
       </c>
       <c r="O2">
-        <v>0.84533394365662</v>
+        <v>0.8453339436572476</v>
       </c>
       <c r="P2">
-        <v>149.220203107533</v>
+        <v>-0.7797968923376495</v>
       </c>
       <c r="Q2">
-        <v>151.2672005251284</v>
+        <v>1.26720052526844</v>
       </c>
     </row>
   </sheetData>
@@ -840,130 +840,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.4040872832273406</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4040872832273414</v>
+        <v>0.6998997052422452</v>
       </c>
       <c r="D2">
-        <v>0.8081745664546819</v>
+        <v>0.6998997052422454</v>
       </c>
       <c r="E2">
-        <v>0.4040872832273406</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.4040872832273411</v>
+        <v>0.699899705242245</v>
       </c>
       <c r="G2">
-        <v>0.808174566454682</v>
+        <v>0.6998997052422454</v>
       </c>
       <c r="H2">
-        <v>4.665998034948193</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>4.665998034948204</v>
+        <v>8.081745664547</v>
       </c>
       <c r="J2">
-        <v>9.331996069896395</v>
+        <v>8.081745664547002</v>
       </c>
       <c r="K2">
-        <v>4.665998034948193</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>4.665998034948199</v>
+        <v>8.081745664546997</v>
       </c>
       <c r="M2">
-        <v>9.331996069896395</v>
+        <v>8.081745664547002</v>
       </c>
       <c r="N2">
-        <v>-4.118843839055381</v>
+        <v>-1.302661710459598E-15</v>
       </c>
       <c r="O2">
-        <v>4.705574442947228</v>
+        <v>5.292305046837607</v>
       </c>
       <c r="P2">
-        <v>1.173461207783683</v>
+        <v>-3.532113235174423</v>
       </c>
       <c r="Q2">
-        <v>4.203752837689607</v>
+        <v>1.302661710459598E-15</v>
       </c>
       <c r="R2">
-        <v>-4.620665444313003</v>
+        <v>-5.037578050934927</v>
       </c>
       <c r="S2">
-        <v>-0.8338252132467865</v>
+        <v>3.786840231077106</v>
       </c>
       <c r="T2">
-        <v>2.709045592378395</v>
+        <v>-3.256654276149013E-15</v>
       </c>
       <c r="U2">
-        <v>1.631860778446838</v>
+        <v>5.972767149283746</v>
       </c>
       <c r="V2">
-        <v>8.681812741650528</v>
+        <v>7.049951963208223</v>
       </c>
       <c r="W2">
-        <v>-2.612706537639466</v>
+        <v>3.256654276149013E-15</v>
       </c>
       <c r="X2">
-        <v>-1.535521723707906</v>
+        <v>-5.683749985066945</v>
       </c>
       <c r="Y2">
-        <v>-8.296456522694815</v>
+        <v>-6.760934798991424</v>
       </c>
       <c r="Z2">
-        <v>6.959586966871044</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>6.959586966871051</v>
+        <v>-173.0404130331012</v>
       </c>
       <c r="AB2">
-        <v>-173.0404130331217</v>
+        <v>6.959586966891396</v>
       </c>
       <c r="AC2">
-        <v>-173.0404130331217</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>-173.0404130331216</v>
+        <v>6.959586966891449</v>
       </c>
       <c r="AE2">
-        <v>6.959586966871023</v>
+        <v>-173.0404130331013</v>
       </c>
       <c r="AF2">
-        <v>1.056556102862494</v>
+        <v>1.100000023840441</v>
       </c>
       <c r="AG2">
-        <v>1.067403369961832</v>
+        <v>0.9874262514315481</v>
       </c>
       <c r="AH2">
-        <v>0.9387871686722089</v>
+        <v>0.9756902409609998</v>
       </c>
       <c r="AI2">
-        <v>1.060763957196372</v>
+        <v>1.100000023840441</v>
       </c>
       <c r="AJ2">
-        <v>1.043533396800563</v>
+        <v>0.9397573987319731</v>
       </c>
       <c r="AK2">
-        <v>0.8935122209068681</v>
+        <v>0.9588546246020166</v>
       </c>
       <c r="AL2">
-        <v>153.6258712172747</v>
+        <v>1.101662640906831E-13</v>
       </c>
       <c r="AM2">
-        <v>26.08578028757464</v>
+        <v>-124.5836849065175</v>
       </c>
       <c r="AN2">
-        <v>-90.73804141981749</v>
+        <v>123.5710235817515</v>
       </c>
       <c r="AO2">
-        <v>155.0979067334024</v>
+        <v>1.103635952584781E-13</v>
       </c>
       <c r="AP2">
-        <v>25.34206720914673</v>
+        <v>-124.5913818981072</v>
       </c>
       <c r="AQ2">
-        <v>-88.77958323315565</v>
+        <v>126.2130370813451</v>
       </c>
     </row>
   </sheetData>
@@ -1112,130 +1112,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0006849323693174558</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0006849323693174584</v>
+        <v>0.001186337663406365</v>
       </c>
       <c r="D2">
-        <v>0.001369864738634913</v>
+        <v>0.001186337663406365</v>
       </c>
       <c r="E2">
-        <v>0.0006849323693174549</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.0006849323693174572</v>
+        <v>0.001186337663406365</v>
       </c>
       <c r="G2">
-        <v>0.001369864738634912</v>
+        <v>0.001186337663406365</v>
       </c>
       <c r="H2">
-        <v>0.007908917756042426</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.007908917756042457</v>
+        <v>0.01369864738634913</v>
       </c>
       <c r="J2">
-        <v>0.01581783551208487</v>
+        <v>0.01369864738634913</v>
       </c>
       <c r="K2">
-        <v>0.007908917756042416</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0.007908917756042442</v>
+        <v>0.01369864738634913</v>
       </c>
       <c r="M2">
-        <v>0.01581783551208486</v>
+        <v>0.01369864738634913</v>
       </c>
       <c r="N2">
-        <v>-0.002157821179309695</v>
+        <v>-6.071531890191943E-18</v>
       </c>
       <c r="O2">
-        <v>0.008023606650719309</v>
+        <v>0.01388939212212891</v>
       </c>
       <c r="P2">
-        <v>0.0117315709428192</v>
+        <v>0.003707964292099922</v>
       </c>
       <c r="Q2">
-        <v>0.002158065128137006</v>
+        <v>4.857225512153554E-18</v>
       </c>
       <c r="R2">
-        <v>-0.008023362701891983</v>
+        <v>-0.01388866027564696</v>
       </c>
       <c r="S2">
-        <v>-0.01173059514750993</v>
+        <v>-0.003707232445617983</v>
       </c>
       <c r="T2">
-        <v>0.008018048856072074</v>
+        <v>-1.423206691556079E-35</v>
       </c>
       <c r="U2">
-        <v>-0.002141964684211938</v>
+        <v>0.003734119487648214</v>
       </c>
       <c r="V2">
-        <v>0.01175216834372031</v>
+        <v>0.01389413302793225</v>
       </c>
       <c r="W2">
-        <v>-0.008017772067983568</v>
+        <v>2.428612756076777E-18</v>
       </c>
       <c r="X2">
-        <v>0.00214224147230043</v>
+        <v>-0.003733289123382724</v>
       </c>
       <c r="Y2">
-        <v>-0.01175106119136633</v>
+        <v>-0.01389330266366676</v>
       </c>
       <c r="Z2">
-        <v>44.93968234855641</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>44.93968234855648</v>
+        <v>-135.0603176514361</v>
       </c>
       <c r="AB2">
+        <v>44.93968234855656</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>44.93968234855658</v>
+      </c>
+      <c r="AE2">
         <v>-135.0603176514362</v>
       </c>
-      <c r="AC2">
-        <v>-135.0603176514363</v>
-      </c>
-      <c r="AD2">
-        <v>-135.0603176514362</v>
-      </c>
-      <c r="AE2">
-        <v>44.93968234855644</v>
-      </c>
       <c r="AF2">
-        <v>1.049869387330141</v>
+        <v>1.049999952316282</v>
       </c>
       <c r="AG2">
-        <v>1.050029087220757</v>
+        <v>1.049927663576826</v>
       </c>
       <c r="AH2">
-        <v>1.049797089600015</v>
+        <v>1.049767948256757</v>
       </c>
       <c r="AI2">
-        <v>1.049843609258966</v>
+        <v>1.049999952316282</v>
       </c>
       <c r="AJ2">
-        <v>1.050008313510063</v>
+        <v>1.049860334070204</v>
       </c>
       <c r="AK2">
-        <v>1.049703970218127</v>
+        <v>1.049695606600145</v>
       </c>
       <c r="AL2">
-        <v>150.0022784719105</v>
+        <v>1.34305045704634E-16</v>
       </c>
       <c r="AM2">
-        <v>29.99269099044328</v>
+        <v>-120.0123410858218</v>
       </c>
       <c r="AN2">
-        <v>-90.01006399193571</v>
+        <v>119.9972465564479</v>
       </c>
       <c r="AO2">
-        <v>150.0044003598864</v>
+        <v>1.382286228788296E-16</v>
       </c>
       <c r="AP2">
-        <v>29.99041181059037</v>
+        <v>-120.0147787920383</v>
       </c>
       <c r="AQ2">
-        <v>-90.01038004812536</v>
+        <v>119.9992109149271</v>
       </c>
     </row>
   </sheetData>
@@ -1384,130 +1384,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0007175117889146635</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0007175117889146659</v>
+        <v>0.001242766873429833</v>
       </c>
       <c r="D2">
-        <v>0.00143502357782933</v>
+        <v>0.001242766873429833</v>
       </c>
       <c r="E2">
-        <v>0.0007175117889146634</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.0007175117889146656</v>
+        <v>0.001242766873429832</v>
       </c>
       <c r="G2">
-        <v>0.001435023577829329</v>
+        <v>0.001242766873429833</v>
       </c>
       <c r="H2">
-        <v>0.008285112489532218</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.008285112489532247</v>
+        <v>0.01435023577829328</v>
       </c>
       <c r="J2">
-        <v>0.01657022497906447</v>
+        <v>0.01435023577829328</v>
       </c>
       <c r="K2">
-        <v>0.008285112489532218</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0.008285112489532242</v>
+        <v>0.01435023577829326</v>
       </c>
       <c r="M2">
-        <v>0.01657022497906446</v>
+        <v>0.01435023577829327</v>
       </c>
       <c r="N2">
-        <v>-0.002368465634527486</v>
+        <v>-6.360652883111716E-18</v>
       </c>
       <c r="O2">
-        <v>0.008805604922260693</v>
+        <v>0.01524274420999385</v>
       </c>
       <c r="P2">
-        <v>0.01287427857546638</v>
+        <v>0.004068673653205685</v>
       </c>
       <c r="Q2">
-        <v>0.002368733342579972</v>
+        <v>5.088522306489372E-18</v>
       </c>
       <c r="R2">
-        <v>-0.008805337214208205</v>
+        <v>-0.01524194108583639</v>
       </c>
       <c r="S2">
-        <v>-0.01287320774325643</v>
+        <v>-0.00406787052904823</v>
       </c>
       <c r="T2">
-        <v>0.008799310099635409</v>
+        <v>-2.544261153244686E-18</v>
       </c>
       <c r="U2">
-        <v>-0.002350334331170224</v>
+        <v>0.004098641437294984</v>
       </c>
       <c r="V2">
-        <v>0.01289795153693041</v>
+        <v>0.01524828586810062</v>
       </c>
       <c r="W2">
-        <v>-0.008799006353964901</v>
+        <v>2.544261153244686E-18</v>
       </c>
       <c r="X2">
-        <v>0.002350638076840728</v>
+        <v>-0.004097730200283462</v>
       </c>
       <c r="Y2">
-        <v>-0.01289673655424838</v>
+        <v>-0.0152473746310891</v>
       </c>
       <c r="Z2">
-        <v>44.93730822262503</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>44.93730822262505</v>
+        <v>-135.0626917773676</v>
       </c>
       <c r="AB2">
+        <v>44.93730822262506</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>44.93730822262508</v>
+      </c>
+      <c r="AE2">
         <v>-135.0626917773677</v>
       </c>
-      <c r="AC2">
-        <v>-135.0626917773677</v>
-      </c>
-      <c r="AD2">
-        <v>-135.0626917773677</v>
-      </c>
-      <c r="AE2">
-        <v>44.93730822262503</v>
-      </c>
       <c r="AF2">
-        <v>1.099863250228142</v>
+        <v>1.100000023841856</v>
       </c>
       <c r="AG2">
-        <v>1.100030538759421</v>
+        <v>1.099924286805659</v>
       </c>
       <c r="AH2">
-        <v>1.09978750377301</v>
+        <v>1.099756982111961</v>
       </c>
       <c r="AI2">
-        <v>1.099836247687821</v>
+        <v>1.100000023841856</v>
       </c>
       <c r="AJ2">
-        <v>1.100008775115283</v>
+        <v>1.099853752771301</v>
       </c>
       <c r="AK2">
-        <v>1.099689954833205</v>
+        <v>1.099681201022603</v>
       </c>
       <c r="AL2">
-        <v>150.0022786513711</v>
+        <v>1.411443044572497E-16</v>
       </c>
       <c r="AM2">
-        <v>29.99269129588945</v>
+        <v>-120.0123402953707</v>
       </c>
       <c r="AN2">
-        <v>-90.01006302180255</v>
+        <v>119.9972472210367</v>
       </c>
       <c r="AO2">
-        <v>150.004400489816</v>
+        <v>1.412633874048473E-16</v>
       </c>
       <c r="AP2">
-        <v>29.99041227879348</v>
+        <v>-120.0147777254427</v>
       </c>
       <c r="AQ2">
-        <v>-90.01037885124788</v>
+        <v>119.9992116433416</v>
       </c>
     </row>
   </sheetData>
@@ -1656,130 +1656,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.3444552667686176</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.3444552667686182</v>
+        <v>0.5966140229781127</v>
       </c>
       <c r="D2">
-        <v>0.6889105335372359</v>
+        <v>0.5966140229781121</v>
       </c>
       <c r="E2">
-        <v>0.3444552667686175</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.344455266768618</v>
+        <v>0.5966140229781126</v>
       </c>
       <c r="G2">
-        <v>0.6889105335372359</v>
+        <v>0.5966140229781121</v>
       </c>
       <c r="H2">
-        <v>3.977426819852915</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>3.977426819852921</v>
+        <v>6.889105335374379</v>
       </c>
       <c r="J2">
-        <v>7.954853639705837</v>
+        <v>6.889105335374372</v>
       </c>
       <c r="K2">
-        <v>3.977426819852913</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>3.97742681985292</v>
+        <v>6.889105335374378</v>
       </c>
       <c r="M2">
-        <v>7.954853639705837</v>
+        <v>6.889105335374372</v>
       </c>
       <c r="N2">
-        <v>-2.964806453325502</v>
+        <v>1.125025984169912E-15</v>
       </c>
       <c r="O2">
-        <v>3.505468163088941</v>
+        <v>4.046129872853336</v>
       </c>
       <c r="P2">
-        <v>1.081323419526883</v>
+        <v>-2.424144743558878</v>
       </c>
       <c r="Q2">
-        <v>3.08326604748496</v>
+        <v>-1.125025984169911E-15</v>
       </c>
       <c r="R2">
-        <v>-3.387008568929485</v>
+        <v>-3.690751090374761</v>
       </c>
       <c r="S2">
-        <v>-0.6074850428890507</v>
+        <v>2.77952352603746</v>
       </c>
       <c r="T2">
-        <v>2.073035574774179</v>
+        <v>-3.937590944594664E-15</v>
       </c>
       <c r="U2">
-        <v>1.089170831134752</v>
+        <v>4.251377237040052</v>
       </c>
       <c r="V2">
-        <v>6.324412811817908</v>
+        <v>5.235241980681923</v>
       </c>
       <c r="W2">
-        <v>-2.003032410175118</v>
+        <v>3.375077952509711E-15</v>
       </c>
       <c r="X2">
-        <v>-1.01916766653569</v>
+        <v>-4.041367743242748</v>
       </c>
       <c r="Y2">
-        <v>-6.044400153421666</v>
+        <v>-5.025232486884618</v>
       </c>
       <c r="Z2">
-        <v>8.646117532419595</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>8.646117532419565</v>
+        <v>-171.3538824675771</v>
       </c>
       <c r="AB2">
-        <v>-171.3538824675731</v>
+        <v>8.646117532415687</v>
       </c>
       <c r="AC2">
-        <v>-171.3538824675731</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>-171.3538824675731</v>
+        <v>8.646117532415655</v>
       </c>
       <c r="AE2">
-        <v>8.646117532419623</v>
+        <v>-171.353882467577</v>
       </c>
       <c r="AF2">
-        <v>0.9095509716098393</v>
+        <v>0.9499999880793201</v>
       </c>
       <c r="AG2">
-        <v>0.9229023361562476</v>
+        <v>0.8519274965731098</v>
       </c>
       <c r="AH2">
-        <v>0.806575137245693</v>
+        <v>0.8374453458530789</v>
       </c>
       <c r="AI2">
-        <v>0.924410264349192</v>
+        <v>0.9499999880793202</v>
       </c>
       <c r="AJ2">
-        <v>0.8892741182221087</v>
+        <v>0.794450311101445</v>
       </c>
       <c r="AK2">
-        <v>0.7636659323896037</v>
+        <v>0.8335929320138662</v>
       </c>
       <c r="AL2">
-        <v>153.6843148703009</v>
+        <v>1.075768492102123E-13</v>
       </c>
       <c r="AM2">
-        <v>25.90646318839084</v>
+        <v>-124.9369014450627</v>
       </c>
       <c r="AN2">
-        <v>-91.05627438102606</v>
+        <v>123.492306249583</v>
       </c>
       <c r="AO2">
-        <v>155.6364982897871</v>
+        <v>1.031665899051294E-13</v>
       </c>
       <c r="AP2">
-        <v>25.39291889708505</v>
+        <v>-123.7575563059327</v>
       </c>
       <c r="AQ2">
-        <v>-87.0930526672006</v>
+        <v>127.5936876756959</v>
       </c>
     </row>
   </sheetData>
@@ -1928,130 +1928,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.3263260376520124</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.3263260376520127</v>
+        <v>0.5652132770460865</v>
       </c>
       <c r="D2">
-        <v>0.652652075304025</v>
+        <v>0.5652132770460857</v>
       </c>
       <c r="E2">
-        <v>0.3263260376520123</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.3263260376520127</v>
+        <v>0.5652132770460864</v>
       </c>
       <c r="G2">
-        <v>0.652652075304025</v>
+        <v>0.5652132770460858</v>
       </c>
       <c r="H2">
-        <v>3.768088513639467</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>3.76808851363947</v>
+        <v>6.526520753042171</v>
       </c>
       <c r="J2">
-        <v>7.536177027278936</v>
+        <v>6.526520753042163</v>
       </c>
       <c r="K2">
-        <v>3.768088513639466</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>3.76808851363947</v>
+        <v>6.52652075304217</v>
       </c>
       <c r="M2">
-        <v>7.536177027278936</v>
+        <v>6.526520753042163</v>
       </c>
       <c r="N2">
-        <v>-2.660934249559561</v>
+        <v>5.022116894809639E-30</v>
       </c>
       <c r="O2">
-        <v>3.146181864735678</v>
+        <v>3.631429479912656</v>
       </c>
       <c r="P2">
-        <v>0.9704952303522371</v>
+        <v>-2.175686634380584</v>
       </c>
       <c r="Q2">
-        <v>2.767252552710266</v>
+        <v>-5.329070377030031E-16</v>
       </c>
       <c r="R2">
-        <v>-3.039863561584975</v>
+        <v>-3.312474570460359</v>
       </c>
       <c r="S2">
-        <v>-0.5452220177494191</v>
+        <v>2.494641543832886</v>
       </c>
       <c r="T2">
-        <v>1.860563732679646</v>
+        <v>-2.664535188514995E-15</v>
       </c>
       <c r="U2">
-        <v>0.9775383364188586</v>
+        <v>3.815640405514114</v>
       </c>
       <c r="V2">
-        <v>5.676204138197054</v>
+        <v>4.69866580177709</v>
       </c>
       <c r="W2">
-        <v>-1.797735409417513</v>
+        <v>2.131628150811996E-15</v>
       </c>
       <c r="X2">
-        <v>-0.9147100131567244</v>
+        <v>-3.627155435727599</v>
       </c>
       <c r="Y2">
-        <v>-5.424890845148519</v>
+        <v>-4.510180831990578</v>
       </c>
       <c r="Z2">
-        <v>8.646117532419566</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>8.646117532419604</v>
+        <v>-171.3538824675771</v>
       </c>
       <c r="AB2">
-        <v>-171.3538824675731</v>
+        <v>8.646117532415687</v>
       </c>
       <c r="AC2">
-        <v>-171.3538824675731</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>-171.3538824675731</v>
+        <v>8.646117532415635</v>
       </c>
       <c r="AE2">
-        <v>8.6461175324196</v>
+        <v>-171.3538824675771</v>
       </c>
       <c r="AF2">
-        <v>0.8616798558268365</v>
+        <v>0.899999976158378</v>
       </c>
       <c r="AG2">
-        <v>0.8743285167997101</v>
+        <v>0.8070891960268606</v>
       </c>
       <c r="AH2">
-        <v>0.7641238035788835</v>
+        <v>0.7933692639570702</v>
       </c>
       <c r="AI2">
-        <v>0.8757570803310026</v>
+        <v>0.8999999761583781</v>
       </c>
       <c r="AJ2">
-        <v>0.8424702055168189</v>
+        <v>0.7526371263392239</v>
       </c>
       <c r="AK2">
-        <v>0.7234729784925249</v>
+        <v>0.7897196087918595</v>
       </c>
       <c r="AL2">
-        <v>153.6843148703009</v>
+        <v>1.079911061164459E-13</v>
       </c>
       <c r="AM2">
-        <v>25.90646318839084</v>
+        <v>-124.9369014450627</v>
       </c>
       <c r="AN2">
-        <v>-91.05627438102606</v>
+        <v>123.492306249583</v>
       </c>
       <c r="AO2">
-        <v>155.6364982897871</v>
+        <v>1.041918507712703E-13</v>
       </c>
       <c r="AP2">
-        <v>25.39291889708505</v>
+        <v>-123.7575563059327</v>
       </c>
       <c r="AQ2">
-        <v>-87.09305266720061</v>
+        <v>127.5936876756959</v>
       </c>
     </row>
   </sheetData>
@@ -2200,130 +2200,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0006196380394547563</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0006196380394547578</v>
+        <v>0.001073244566638008</v>
       </c>
       <c r="D2">
-        <v>0.001239276078909514</v>
+        <v>0.001073244566638008</v>
       </c>
       <c r="E2">
-        <v>0.0006196380394547563</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.0006196380394547576</v>
+        <v>0.001073244566638009</v>
       </c>
       <c r="G2">
-        <v>0.001239276078909514</v>
+        <v>0.001073244566638008</v>
       </c>
       <c r="H2">
-        <v>0.007154963777586711</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.007154963777586727</v>
+        <v>0.01239276078909515</v>
       </c>
       <c r="J2">
-        <v>0.01430992755517344</v>
+        <v>0.01239276078909514</v>
       </c>
       <c r="K2">
-        <v>0.007154963777586711</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0.007154963777586726</v>
+        <v>0.01239276078909515</v>
       </c>
       <c r="M2">
-        <v>0.01430992755517344</v>
+        <v>0.01239276078909515</v>
       </c>
       <c r="N2">
-        <v>-0.001766293228923376</v>
+        <v>-2.746645469164095E-19</v>
       </c>
       <c r="O2">
-        <v>0.00656743392210079</v>
+        <v>0.01136857461527819</v>
       </c>
       <c r="P2">
-        <v>0.00960228138635481</v>
+        <v>0.003034847464254063</v>
       </c>
       <c r="Q2">
-        <v>0.001766676565909142</v>
+        <v>-2.746645469164096E-19</v>
       </c>
       <c r="R2">
-        <v>-0.006567050585115019</v>
+        <v>-0.01136742460432089</v>
       </c>
       <c r="S2">
-        <v>-0.009600748038411735</v>
+        <v>-0.003033697453296759</v>
       </c>
       <c r="T2">
-        <v>0.006562798547113946</v>
+        <v>-6.591949125993829E-18</v>
       </c>
       <c r="U2">
-        <v>-0.001753174491071127</v>
+        <v>0.003056449564971676</v>
       </c>
       <c r="V2">
-        <v>0.009619248112085659</v>
+        <v>0.01137242260315677</v>
       </c>
       <c r="W2">
-        <v>-0.006562572015845609</v>
+        <v>7.690607313659468E-18</v>
       </c>
       <c r="X2">
-        <v>0.001753401022339462</v>
+        <v>-0.003055769971166663</v>
       </c>
       <c r="Y2">
-        <v>-0.009618341987012311</v>
+        <v>-0.01137174300935176</v>
       </c>
       <c r="Z2">
-        <v>44.93890368369447</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>44.93890368369449</v>
+        <v>-135.0610963162982</v>
       </c>
       <c r="AB2">
+        <v>44.9389036836945</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>44.93890368369448</v>
+      </c>
+      <c r="AE2">
         <v>-135.0610963162982</v>
       </c>
-      <c r="AC2">
-        <v>-135.0610963162982</v>
-      </c>
-      <c r="AD2">
-        <v>-135.0610963162982</v>
-      </c>
-      <c r="AE2">
-        <v>44.93890368369448</v>
-      </c>
       <c r="AF2">
-        <v>0.9498763823371305</v>
+        <v>0.9499999880790745</v>
       </c>
       <c r="AG2">
-        <v>0.950027443029968</v>
+        <v>0.9499312985903279</v>
       </c>
       <c r="AH2">
-        <v>0.9498076839092953</v>
+        <v>0.9497802226059048</v>
       </c>
       <c r="AI2">
-        <v>0.9498597353478833</v>
+        <v>0.9499999880790745</v>
       </c>
       <c r="AJ2">
-        <v>0.9499838462230716</v>
+        <v>0.9498274465944992</v>
       </c>
       <c r="AK2">
-        <v>0.9496871683818496</v>
+        <v>0.9497033152804071</v>
       </c>
       <c r="AL2">
-        <v>150.0023929725074</v>
+        <v>1.524826437889376E-16</v>
       </c>
       <c r="AM2">
-        <v>29.99234777609244</v>
+        <v>-120.0129131626926</v>
       </c>
       <c r="AN2">
-        <v>-90.01052169766021</v>
+        <v>119.9971322138701</v>
       </c>
       <c r="AO2">
-        <v>150.0060099968997</v>
+        <v>1.404779204971012E-16</v>
       </c>
       <c r="AP2">
-        <v>29.98966943394219</v>
+        <v>-120.0146543330407</v>
       </c>
       <c r="AQ2">
-        <v>-90.00864540853833</v>
+        <v>120.0016883560015</v>
       </c>
     </row>
   </sheetData>
@@ -2472,130 +2472,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0005870255028777344</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.000587025502877736</v>
+        <v>0.001016757996322908</v>
       </c>
       <c r="D2">
-        <v>0.001174051005755471</v>
+        <v>0.001016757996322908</v>
       </c>
       <c r="E2">
-        <v>0.0005870255028777343</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.000587025502877736</v>
+        <v>0.001016757996322908</v>
       </c>
       <c r="G2">
-        <v>0.00117405100575547</v>
+        <v>0.001016757996322908</v>
       </c>
       <c r="H2">
-        <v>0.006778386642152708</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.006778386642152727</v>
+        <v>0.01174051005755471</v>
       </c>
       <c r="J2">
-        <v>0.01355677328430544</v>
+        <v>0.01174051005755471</v>
       </c>
       <c r="K2">
-        <v>0.006778386642152707</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0.006778386642152727</v>
+        <v>0.01174051005755471</v>
       </c>
       <c r="M2">
-        <v>0.01355677328430544</v>
+        <v>0.01174051005755471</v>
       </c>
       <c r="N2">
-        <v>-0.001585260360700975</v>
+        <v>2.602085145033502E-19</v>
       </c>
       <c r="O2">
-        <v>0.005894317261565491</v>
+        <v>0.01020337416243</v>
       </c>
       <c r="P2">
-        <v>0.00861811380172902</v>
+        <v>0.002723796540163565</v>
       </c>
       <c r="Q2">
-        <v>0.001585604408290796</v>
+        <v>-1.301042572516751E-18</v>
       </c>
       <c r="R2">
-        <v>-0.00589397321397567</v>
+        <v>-0.01020234201966054</v>
       </c>
       <c r="S2">
-        <v>-0.008616737611369732</v>
+        <v>-0.002722764397394105</v>
       </c>
       <c r="T2">
-        <v>0.005890156980529871</v>
+        <v>-9.367506522120607E-18</v>
       </c>
       <c r="U2">
-        <v>-0.001573486202956914</v>
+        <v>0.002743184574616021</v>
       </c>
       <c r="V2">
-        <v>0.00863334155514593</v>
+        <v>0.01020682775810283</v>
       </c>
       <c r="W2">
-        <v>-0.00588995366715343</v>
+        <v>8.326672464107207E-18</v>
       </c>
       <c r="X2">
-        <v>0.001573689516333354</v>
+        <v>-0.002742574634486702</v>
       </c>
       <c r="Y2">
-        <v>-0.008632528301640175</v>
+        <v>-0.01020621781797352</v>
       </c>
       <c r="Z2">
-        <v>44.93890368369445</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>44.93890368369445</v>
+        <v>-135.0610963162982</v>
       </c>
       <c r="AB2">
+        <v>44.93890368369449</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>44.93890368369448</v>
+      </c>
+      <c r="AE2">
         <v>-135.0610963162982</v>
       </c>
-      <c r="AC2">
-        <v>-135.0610963162982</v>
-      </c>
-      <c r="AD2">
-        <v>-135.0610963162983</v>
-      </c>
-      <c r="AE2">
-        <v>44.93890368369447</v>
-      </c>
       <c r="AF2">
-        <v>0.8998828759831994</v>
+        <v>0.8999999761581453</v>
       </c>
       <c r="AG2">
-        <v>0.9000259861112606</v>
+        <v>0.8999349019065559</v>
       </c>
       <c r="AH2">
-        <v>0.8998177932629997</v>
+        <v>0.8997917772917293</v>
       </c>
       <c r="AI2">
-        <v>0.8998671051515009</v>
+        <v>0.8999999761581453</v>
       </c>
       <c r="AJ2">
-        <v>0.8999846838737243</v>
+        <v>0.8998365158066162</v>
       </c>
       <c r="AK2">
-        <v>0.8997036206596432</v>
+        <v>0.8997189177212213</v>
       </c>
       <c r="AL2">
-        <v>150.0023929725074</v>
+        <v>1.527455349910262E-16</v>
       </c>
       <c r="AM2">
-        <v>29.99234777609244</v>
+        <v>-120.0129131626926</v>
       </c>
       <c r="AN2">
-        <v>-90.01052169766021</v>
+        <v>119.9971322138701</v>
       </c>
       <c r="AO2">
-        <v>150.0060099968997</v>
+        <v>1.409029317086447E-16</v>
       </c>
       <c r="AP2">
-        <v>29.98966943394218</v>
+        <v>-120.0146543330407</v>
       </c>
       <c r="AQ2">
-        <v>-90.00864540853833</v>
+        <v>120.0016883560015</v>
       </c>
     </row>
   </sheetData>
@@ -2747,130 +2747,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.494622066747603</v>
+        <v>0.571140366767305</v>
       </c>
       <c r="C2">
-        <v>0.4946220667476021</v>
+        <v>0.2855701833836528</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.2855701833836526</v>
       </c>
       <c r="E2">
-        <v>0.4946220667476029</v>
+        <v>0.5711403667673045</v>
       </c>
       <c r="F2">
-        <v>0.4946220667476018</v>
+        <v>0.2855701833836528</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.2855701833836525</v>
       </c>
       <c r="H2">
-        <v>5.711403667677153</v>
+        <v>6.594960889963303</v>
       </c>
       <c r="I2">
-        <v>5.711403667677142</v>
+        <v>3.297480444981654</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>3.297480444981653</v>
       </c>
       <c r="K2">
-        <v>5.711403667677152</v>
+        <v>6.594960889963297</v>
       </c>
       <c r="L2">
-        <v>5.711403667677139</v>
+        <v>3.297480444981654</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.297480444981652</v>
       </c>
       <c r="N2">
-        <v>3.55277372596467</v>
+        <v>0.765888240851003</v>
       </c>
       <c r="O2">
-        <v>-2.403941364674858</v>
+        <v>-2.786885485105858</v>
       </c>
       <c r="P2">
-        <v>5.029219354689502E-15</v>
+        <v>3.169829605531358</v>
       </c>
       <c r="Q2">
-        <v>-3.42555520910474</v>
+        <v>-0.5962635517046704</v>
       </c>
       <c r="R2">
-        <v>2.531159881534784</v>
+        <v>2.829291657392439</v>
       </c>
       <c r="S2">
-        <v>-4.800114021666379E-15</v>
+        <v>-3.127423433244775</v>
       </c>
       <c r="T2">
-        <v>4.247048387870104</v>
+        <v>6.125206376130295</v>
       </c>
       <c r="U2">
-        <v>4.940761176327763</v>
+        <v>1.878157988257543</v>
       </c>
       <c r="V2">
-        <v>-1.065365980208625E-15</v>
+        <v>1.184445199807613</v>
       </c>
       <c r="W2">
-        <v>-4.10270430353609</v>
+        <v>-5.932747597018549</v>
       </c>
       <c r="X2">
-        <v>-4.796417091993757</v>
+        <v>-1.830043293479612</v>
       </c>
       <c r="Y2">
-        <v>1.59001786579263E-15</v>
+        <v>-1.136330505029679</v>
       </c>
       <c r="Z2">
-        <v>96.64268332535339</v>
+        <v>-83.3573166747358</v>
       </c>
       <c r="AA2">
-        <v>-83.35731667463929</v>
+        <v>96.64268332525687</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>96.6426833252569</v>
       </c>
       <c r="AC2">
-        <v>-83.35731667463932</v>
+        <v>96.64268332525687</v>
       </c>
       <c r="AD2">
-        <v>96.64268332535342</v>
+        <v>-83.35731667473578</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>-83.35731667473581</v>
       </c>
       <c r="AG2">
-        <v>0.9694837543973714</v>
+        <v>0.9360030528625817</v>
       </c>
       <c r="AH2">
-        <v>0.9620310662051977</v>
+        <v>1.019167731432679</v>
       </c>
       <c r="AI2">
-        <v>1.049999952317102</v>
+        <v>1.026205555670933</v>
       </c>
       <c r="AJ2">
-        <v>0.9358074645720132</v>
+        <v>0.9041199457001776</v>
       </c>
       <c r="AK2">
-        <v>0.9495597156065237</v>
+        <v>1.021859660291051</v>
       </c>
       <c r="AL2">
-        <v>1.049999952317102</v>
+        <v>1.009093217981268</v>
       </c>
       <c r="AM2">
-        <v>146.7292669372943</v>
+        <v>-0.4845199157074085</v>
       </c>
       <c r="AN2">
-        <v>32.58805277812628</v>
+        <v>-117.3344192926456</v>
       </c>
       <c r="AO2">
-        <v>-89.99999999997044</v>
+        <v>117.1314939235704</v>
       </c>
       <c r="AP2">
-        <v>146.7824713477574</v>
+        <v>0.9035130070360725</v>
       </c>
       <c r="AQ2">
-        <v>34.4641404930511</v>
+        <v>-116.2529256224295</v>
       </c>
       <c r="AR2">
-        <v>-89.99999999997044</v>
+        <v>116.6109930357102</v>
       </c>
     </row>
   </sheetData>
@@ -3022,130 +3022,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.4977679068497734</v>
+        <v>0.5747728700271006</v>
       </c>
       <c r="C2">
-        <v>0.4977679068497727</v>
+        <v>0.2873864350135502</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.2873864350135503</v>
       </c>
       <c r="E2">
-        <v>0.4977679068497734</v>
+        <v>0.5747728700271004</v>
       </c>
       <c r="F2">
-        <v>0.4977679068497725</v>
+        <v>0.2873864350135502</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.2873864350135502</v>
       </c>
       <c r="H2">
-        <v>5.747728700273464</v>
+        <v>6.636905424660807</v>
       </c>
       <c r="I2">
-        <v>5.747728700273457</v>
+        <v>3.318452712330402</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>3.318452712330403</v>
       </c>
       <c r="K2">
-        <v>5.747728700273464</v>
+        <v>6.636905424660805</v>
       </c>
       <c r="L2">
-        <v>5.747728700273455</v>
+        <v>3.318452712330402</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.318452712330402</v>
       </c>
       <c r="N2">
-        <v>3.743568431118637</v>
+        <v>0.8044172768846573</v>
       </c>
       <c r="O2">
-        <v>-2.536942515790369</v>
+        <v>-2.939151154232582</v>
       </c>
       <c r="P2">
-        <v>1.41407787363516E-15</v>
+        <v>3.341359792674915</v>
       </c>
       <c r="Q2">
-        <v>-3.614726526133725</v>
+        <v>-0.6326280702382592</v>
       </c>
       <c r="R2">
-        <v>2.665784420775275</v>
+        <v>2.982098455894181</v>
       </c>
       <c r="S2">
-        <v>-1.853734290837047E-15</v>
+        <v>-3.298412491013314</v>
       </c>
       <c r="T2">
-        <v>4.503379368674304</v>
+        <v>6.489484672134044</v>
       </c>
       <c r="U2">
-        <v>5.230847639528414</v>
+        <v>1.986105303460184</v>
       </c>
       <c r="V2">
-        <v>-2.069381868496651E-16</v>
+        <v>1.258637032606843</v>
       </c>
       <c r="W2">
-        <v>-4.357193363225324</v>
+        <v>-6.294569998202233</v>
       </c>
       <c r="X2">
-        <v>-5.084661634079442</v>
+        <v>-1.937376634977235</v>
       </c>
       <c r="Y2">
-        <v>7.098673273907309E-16</v>
+        <v>-1.209908364123894</v>
       </c>
       <c r="Z2">
-        <v>96.607096937726</v>
+        <v>-83.39290306229678</v>
       </c>
       <c r="AA2">
-        <v>-83.39290306226677</v>
+        <v>96.60709693769593</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>96.60709693769596</v>
       </c>
       <c r="AC2">
-        <v>-83.39290306226674</v>
+        <v>96.60709693769594</v>
       </c>
       <c r="AD2">
-        <v>96.60709693772594</v>
+        <v>-83.39290306229677</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>-83.39290306229677</v>
       </c>
       <c r="AG2">
-        <v>1.018866857568214</v>
+        <v>0.9852711143705776</v>
       </c>
       <c r="AH2">
-        <v>1.011458899805064</v>
+        <v>1.068957224502451</v>
       </c>
       <c r="AI2">
-        <v>1.10000002384268</v>
+        <v>1.075969383984518</v>
       </c>
       <c r="AJ2">
-        <v>0.9849793337675831</v>
+        <v>0.9531973822794995</v>
       </c>
       <c r="AK2">
-        <v>0.99884614063114</v>
+        <v>1.071634739120153</v>
       </c>
       <c r="AL2">
-        <v>1.10000002384268</v>
+        <v>1.058721724243257</v>
       </c>
       <c r="AM2">
-        <v>146.8710330066951</v>
+        <v>-0.4590737163044236</v>
       </c>
       <c r="AN2">
-        <v>32.48031732119983</v>
+        <v>-117.4414148648204</v>
       </c>
       <c r="AO2">
-        <v>-89.99999999997148</v>
+        <v>117.2476897471196</v>
       </c>
       <c r="AP2">
-        <v>146.9280048930788</v>
+        <v>0.8679266195802701</v>
       </c>
       <c r="AQ2">
-        <v>34.27420324489271</v>
+        <v>-116.4034326336533</v>
       </c>
       <c r="AR2">
-        <v>-89.99999999997148</v>
+        <v>116.750909830372</v>
       </c>
     </row>
   </sheetData>
@@ -3297,130 +3297,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0003957313133778661</v>
+        <v>0.0004569511606109506</v>
       </c>
       <c r="C2">
-        <v>0.0003957313133778661</v>
+        <v>0.0002284755803054753</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.0002284755803054752</v>
       </c>
       <c r="E2">
-        <v>0.0003957313133778661</v>
+        <v>0.0004569511606109504</v>
       </c>
       <c r="F2">
-        <v>0.0003957313133778657</v>
+        <v>0.0002284755803054752</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.0002284755803054752</v>
       </c>
       <c r="H2">
-        <v>0.004569511606109504</v>
+        <v>0.005276417511704884</v>
       </c>
       <c r="I2">
-        <v>0.004569511606109504</v>
+        <v>0.002638208755852443</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.002638208755852442</v>
       </c>
       <c r="K2">
-        <v>0.004569511606109503</v>
+        <v>0.005276417511704883</v>
       </c>
       <c r="L2">
-        <v>0.004569511606109499</v>
+        <v>0.002638208755852442</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.002638208755852441</v>
       </c>
       <c r="N2">
-        <v>0.004633865533505802</v>
+        <v>0.003915571942978053</v>
       </c>
       <c r="O2">
-        <v>0.001239492380961274</v>
+        <v>-0.000718293590527755</v>
       </c>
       <c r="P2">
-        <v>3.249452738643773E-18</v>
+        <v>0.00267607956201678</v>
       </c>
       <c r="Q2">
-        <v>-0.00463378409980248</v>
+        <v>-0.003915463364706958</v>
       </c>
       <c r="R2">
-        <v>-0.001239410947257949</v>
+        <v>0.0007183207350955283</v>
       </c>
       <c r="S2">
-        <v>-3.447433000746205E-18</v>
+        <v>-0.002676052417449006</v>
       </c>
       <c r="T2">
-        <v>0.001243749743917568</v>
+        <v>0.003919002494631661</v>
       </c>
       <c r="U2">
-        <v>0.004634753998029916</v>
+        <v>0.002675252750714092</v>
       </c>
       <c r="V2">
-        <v>-2.890820484474955E-18</v>
+        <v>-0.0007157515033982626</v>
       </c>
       <c r="W2">
-        <v>-0.001243657347986298</v>
+        <v>-0.003918879300056631</v>
       </c>
       <c r="X2">
-        <v>-0.004634661602098643</v>
+        <v>-0.002675221952070334</v>
       </c>
       <c r="Y2">
-        <v>1.808055548547357E-18</v>
+        <v>0.0007157823020420175</v>
       </c>
       <c r="Z2">
+        <v>-45.02844700218296</v>
+      </c>
+      <c r="AA2">
+        <v>134.9715529978097</v>
+      </c>
+      <c r="AB2">
         <v>134.9715529978098</v>
       </c>
-      <c r="AA2">
-        <v>-45.02844700218287</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
       <c r="AC2">
-        <v>-45.02844700218289</v>
+        <v>134.9715529978098</v>
       </c>
       <c r="AD2">
-        <v>134.9715529978098</v>
+        <v>-45.02844700218298</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>-45.02844700218296</v>
       </c>
       <c r="AG2">
-        <v>1.049975875229383</v>
+        <v>1.049932313230428</v>
       </c>
       <c r="AH2">
-        <v>1.049922570914869</v>
+        <v>1.049956391316273</v>
       </c>
       <c r="AI2">
-        <v>1.049999952316285</v>
+        <v>1.050009693913876</v>
       </c>
       <c r="AJ2">
-        <v>1.049953421801627</v>
+        <v>1.049901251880345</v>
       </c>
       <c r="AK2">
-        <v>1.049898433196768</v>
+        <v>1.049947784707017</v>
       </c>
       <c r="AL2">
-        <v>1.049999952316285</v>
+        <v>1.050002770727339</v>
       </c>
       <c r="AM2">
-        <v>149.9958827930338</v>
+        <v>-0.003358706686870693</v>
       </c>
       <c r="AN2">
-        <v>29.99907930920909</v>
+        <v>-119.9992413462975</v>
       </c>
       <c r="AO2">
-        <v>-89.99999999999629</v>
+        <v>119.9975621552268</v>
       </c>
       <c r="AP2">
-        <v>149.9950692041297</v>
+        <v>-0.003464859508877286</v>
       </c>
       <c r="AQ2">
-        <v>29.99973375089488</v>
+        <v>-119.9985338836107</v>
       </c>
       <c r="AR2">
-        <v>-89.99999999999629</v>
+        <v>119.9968016981316</v>
       </c>
     </row>
   </sheetData>
@@ -3491,10 +3491,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.8081745664560922</v>
+        <v>0.8081745664566463</v>
       </c>
       <c r="C2">
-        <v>0.8081745664560922</v>
+        <v>0.8081745664566463</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -3503,40 +3503,40 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>27.99598820973803</v>
+        <v>27.99598820975723</v>
       </c>
       <c r="G2">
-        <v>27.99598820973803</v>
+        <v>27.99598820975723</v>
       </c>
       <c r="H2">
-        <v>3.520383623374679</v>
+        <v>3.520383623275734</v>
       </c>
       <c r="I2">
-        <v>-2.501475639760471</v>
+        <v>-2.501475639660106</v>
       </c>
       <c r="J2">
-        <v>26.04543822497919</v>
+        <v>26.04543822501815</v>
       </c>
       <c r="K2">
-        <v>-24.88936956810797</v>
+        <v>-24.8893695681453</v>
       </c>
       <c r="L2">
-        <v>66.95958696689567</v>
+        <v>-83.04041303320908</v>
       </c>
       <c r="M2">
-        <v>-113.0404130330971</v>
+        <v>96.95958696678363</v>
       </c>
       <c r="N2">
-        <v>0.9387871686716606</v>
+        <v>0.9387871686719225</v>
       </c>
       <c r="O2">
-        <v>0.8935122209062168</v>
+        <v>0.8935122209065726</v>
       </c>
       <c r="P2">
-        <v>149.2619585801569</v>
+        <v>-0.7380414197227489</v>
       </c>
       <c r="Q2">
-        <v>151.2204167668213</v>
+        <v>1.22041676695381</v>
       </c>
     </row>
   </sheetData>
@@ -3688,130 +3688,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.00041456515501305</v>
+        <v>0.0004786986076868466</v>
       </c>
       <c r="C2">
-        <v>0.00041456515501305</v>
+        <v>0.0002393493038434232</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.0002393493038434232</v>
       </c>
       <c r="E2">
-        <v>0.0004145651550130499</v>
+        <v>0.0004786986076868468</v>
       </c>
       <c r="F2">
-        <v>0.0004145651550130497</v>
+        <v>0.0002393493038434231</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.0002393493038434233</v>
       </c>
       <c r="H2">
-        <v>0.004786986076868467</v>
+        <v>0.005527535400173999</v>
       </c>
       <c r="I2">
-        <v>0.004786986076868466</v>
+        <v>0.002763767700086999</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.002763767700086999</v>
       </c>
       <c r="K2">
-        <v>0.004786986076868466</v>
+        <v>0.005527535400174002</v>
       </c>
       <c r="L2">
-        <v>0.004786986076868465</v>
+        <v>0.002763767700086997</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.002763767700087</v>
       </c>
       <c r="N2">
-        <v>0.005085536816848565</v>
+        <v>0.004297164536587285</v>
       </c>
       <c r="O2">
-        <v>0.001360209988032357</v>
+        <v>-0.0007883722802612807</v>
       </c>
       <c r="P2">
-        <v>1.237827417053928E-18</v>
+        <v>0.002936954548554924</v>
       </c>
       <c r="Q2">
-        <v>-0.005085447447427488</v>
+        <v>-0.004297045377359189</v>
       </c>
       <c r="R2">
-        <v>-0.001360120618611282</v>
+        <v>0.0007884020700683049</v>
       </c>
       <c r="S2">
-        <v>-5.019890603933573E-19</v>
+        <v>-0.0029369247587479</v>
       </c>
       <c r="T2">
-        <v>0.001365093416772357</v>
+        <v>0.004301107910704865</v>
       </c>
       <c r="U2">
-        <v>0.005086568449284943</v>
+        <v>0.002936014493932512</v>
       </c>
       <c r="V2">
-        <v>-9.820151038674606E-19</v>
+        <v>-0.0007854605385800801</v>
       </c>
       <c r="W2">
-        <v>-0.001364992016853768</v>
+        <v>-0.004300972710813414</v>
       </c>
       <c r="X2">
-        <v>-0.005086467049366354</v>
+        <v>-0.002935980693959648</v>
       </c>
       <c r="Y2">
-        <v>-8.471391059962761E-20</v>
+        <v>0.000785494338552944</v>
       </c>
       <c r="Z2">
+        <v>-45.02963576259393</v>
+      </c>
+      <c r="AA2">
         <v>134.9703642373988</v>
       </c>
-      <c r="AA2">
-        <v>-45.0296357625939</v>
-      </c>
       <c r="AB2">
-        <v>0</v>
+        <v>134.9703642373988</v>
       </c>
       <c r="AC2">
-        <v>-45.02963576259392</v>
+        <v>134.9703642373988</v>
       </c>
       <c r="AD2">
-        <v>134.9703642373988</v>
+        <v>-45.02963576259391</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>-45.02963576259391</v>
       </c>
       <c r="AG2">
-        <v>1.099974799226225</v>
+        <v>1.099929164305093</v>
       </c>
       <c r="AH2">
-        <v>1.099918959299556</v>
+        <v>1.099954389967246</v>
       </c>
       <c r="AI2">
-        <v>1.100000023841859</v>
+        <v>1.100010228095345</v>
       </c>
       <c r="AJ2">
-        <v>1.099951276859666</v>
+        <v>1.099896624625498</v>
       </c>
       <c r="AK2">
-        <v>1.099893673067847</v>
+        <v>1.099945374029749</v>
       </c>
       <c r="AL2">
-        <v>1.100000023841859</v>
+        <v>1.100002975114147</v>
       </c>
       <c r="AM2">
-        <v>149.9958829249117</v>
+        <v>-0.003358544756655578</v>
       </c>
       <c r="AN2">
-        <v>29.99907942021756</v>
+        <v>-119.9992413162576</v>
       </c>
       <c r="AO2">
-        <v>-89.99999999999629</v>
+        <v>119.9975622061431</v>
       </c>
       <c r="AP2">
-        <v>149.9950693821049</v>
+        <v>-0.003464659707758895</v>
       </c>
       <c r="AQ2">
-        <v>29.99973387260436</v>
+        <v>-119.9985338618044</v>
       </c>
       <c r="AR2">
-        <v>-89.99999999999629</v>
+        <v>119.9968017762087</v>
       </c>
     </row>
   </sheetData>
@@ -3963,130 +3963,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.4256783984533926</v>
+        <v>0.4915310758706932</v>
       </c>
       <c r="C2">
-        <v>0.4256783984533923</v>
+        <v>0.2457655379353464</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.2457655379353465</v>
       </c>
       <c r="E2">
-        <v>0.4256783984533928</v>
+        <v>0.4915310758706931</v>
       </c>
       <c r="F2">
-        <v>0.4256783984533923</v>
+        <v>0.2457655379353465</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.2457655379353466</v>
       </c>
       <c r="H2">
-        <v>4.9153107587055</v>
+        <v>5.675711979380222</v>
       </c>
       <c r="I2">
-        <v>4.915310758705497</v>
+        <v>2.837855989690109</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>2.83785598969011</v>
       </c>
       <c r="K2">
-        <v>4.915310758705502</v>
+        <v>5.675711979380221</v>
       </c>
       <c r="L2">
-        <v>4.915310758705497</v>
+        <v>2.83785598969011</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.837855989690111</v>
       </c>
       <c r="N2">
-        <v>2.841920172524526</v>
+        <v>0.705093592537738</v>
       </c>
       <c r="O2">
-        <v>-1.784279783710212</v>
+        <v>-2.136826579986562</v>
       </c>
       <c r="P2">
-        <v>3.132098991077404E-15</v>
+        <v>2.489373376255434</v>
       </c>
       <c r="Q2">
-        <v>-2.661007993240288</v>
+        <v>-0.4638773534919449</v>
       </c>
       <c r="R2">
-        <v>1.965191962994448</v>
+        <v>2.197130639748011</v>
       </c>
       <c r="S2">
-        <v>-2.950433842451329E-15</v>
+        <v>-2.429069316493987</v>
       </c>
       <c r="T2">
-        <v>3.25116812258503</v>
+        <v>4.758067171883171</v>
       </c>
       <c r="U2">
-        <v>3.885932635227683</v>
+        <v>1.5068990492899</v>
       </c>
       <c r="V2">
-        <v>-4.656859501806438E-16</v>
+        <v>0.8721345366516914</v>
       </c>
       <c r="W2">
-        <v>-3.144258883580187</v>
+        <v>-4.615521519876627</v>
       </c>
       <c r="X2">
-        <v>-3.779023396222845</v>
+        <v>-1.471262636288267</v>
       </c>
       <c r="Y2">
-        <v>3.581262191056622E-16</v>
+        <v>-0.8364981236500576</v>
       </c>
       <c r="Z2">
-        <v>97.81281237388018</v>
+        <v>-82.18718762616595</v>
       </c>
       <c r="AA2">
-        <v>-82.18718762611252</v>
+        <v>97.81281237382679</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>97.81281237382673</v>
       </c>
       <c r="AC2">
-        <v>-82.18718762611253</v>
+        <v>97.81281237382674</v>
       </c>
       <c r="AD2">
-        <v>97.81281237388021</v>
+        <v>-82.18718762616592</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>-82.18718762616599</v>
       </c>
       <c r="AG2">
-        <v>0.8785144284484432</v>
+        <v>0.8474755350167545</v>
       </c>
       <c r="AH2">
-        <v>0.8699336534230577</v>
+        <v>0.9213724321954138</v>
       </c>
       <c r="AI2">
-        <v>0.94999998807871</v>
+        <v>0.9294784550723214</v>
       </c>
       <c r="AJ2">
-        <v>0.8380226186463287</v>
+        <v>0.8173025129136731</v>
       </c>
       <c r="AK2">
-        <v>0.8665697754548274</v>
+        <v>0.931773290882539</v>
       </c>
       <c r="AL2">
-        <v>0.94999998807871</v>
+        <v>0.9052845957116366</v>
       </c>
       <c r="AM2">
-        <v>146.6553654464649</v>
+        <v>-0.6164514392171095</v>
       </c>
       <c r="AN2">
-        <v>32.47568898723158</v>
+        <v>-117.37883833194</v>
       </c>
       <c r="AO2">
-        <v>-90.00000000000878</v>
+        <v>117.1203644707401</v>
       </c>
       <c r="AP2">
-        <v>147.5713439924405</v>
+        <v>2.073642055958753</v>
       </c>
       <c r="AQ2">
-        <v>35.28843500952932</v>
+        <v>-115.9946037575568</v>
       </c>
       <c r="AR2">
-        <v>-90.00000000000878</v>
+        <v>116.8149734530221</v>
       </c>
     </row>
   </sheetData>
@@ -4238,130 +4238,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.4032742665963086</v>
+        <v>0.4656610127533912</v>
       </c>
       <c r="C2">
-        <v>0.4032742665963083</v>
+        <v>0.2328305063766954</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.2328305063766955</v>
       </c>
       <c r="E2">
-        <v>0.4032742665963088</v>
+        <v>0.4656610127533912</v>
       </c>
       <c r="F2">
-        <v>0.4032742665963083</v>
+        <v>0.2328305063766956</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.2328305063766955</v>
       </c>
       <c r="H2">
-        <v>4.656610127532554</v>
+        <v>5.376990221285683</v>
       </c>
       <c r="I2">
-        <v>4.656610127532551</v>
+        <v>2.68849511064284</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>2.688495110642841</v>
       </c>
       <c r="K2">
-        <v>4.656610127532556</v>
+        <v>5.376990221285683</v>
       </c>
       <c r="L2">
-        <v>4.65661012753255</v>
+        <v>2.688495110642841</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.688495110642841</v>
       </c>
       <c r="N2">
-        <v>2.550642964603157</v>
+        <v>0.6328263645757342</v>
       </c>
       <c r="O2">
-        <v>-1.601403417732634</v>
+        <v>-1.917816600027218</v>
       </c>
       <c r="P2">
-        <v>3.236961593251428E-15</v>
+        <v>2.234229782315088</v>
       </c>
       <c r="Q2">
-        <v>-2.388273035368846</v>
+        <v>-0.4163331255965276</v>
       </c>
       <c r="R2">
-        <v>1.763773346966942</v>
+        <v>1.97193990977202</v>
       </c>
       <c r="S2">
-        <v>-3.424258166687014E-15</v>
+        <v>-2.180106472570286</v>
       </c>
       <c r="T2">
-        <v>2.917945823667216</v>
+        <v>4.27039811828786</v>
       </c>
       <c r="U2">
-        <v>3.487651353753761</v>
+        <v>1.352452294613245</v>
       </c>
       <c r="V2">
-        <v>-1.232774664691337E-15</v>
+        <v>0.7827467645306886</v>
       </c>
       <c r="W2">
-        <v>-2.821994043967313</v>
+        <v>-4.142462412021247</v>
       </c>
       <c r="X2">
-        <v>-3.391699574053864</v>
+        <v>-1.320468368046596</v>
       </c>
       <c r="Y2">
-        <v>1.234253487293286E-15</v>
+        <v>-0.7507628379640363</v>
       </c>
       <c r="Z2">
-        <v>97.81281237388021</v>
+        <v>-82.18718762616599</v>
       </c>
       <c r="AA2">
-        <v>-82.18718762611253</v>
+        <v>97.81281237382673</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>97.81281237382673</v>
       </c>
       <c r="AC2">
-        <v>-82.1871876261125</v>
+        <v>97.81281237382673</v>
       </c>
       <c r="AD2">
-        <v>97.81281237388019</v>
+        <v>-82.18718762616594</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>-82.18718762616597</v>
       </c>
       <c r="AG2">
-        <v>0.832276815347048</v>
+        <v>0.8028715482954342</v>
       </c>
       <c r="AH2">
-        <v>0.8241476601731822</v>
+        <v>0.8728791341201809</v>
       </c>
       <c r="AI2">
-        <v>0.8999999761577999</v>
+        <v>0.8805585241070227</v>
       </c>
       <c r="AJ2">
-        <v>0.7939161539641028</v>
+        <v>0.7742865803858006</v>
       </c>
       <c r="AK2">
-        <v>0.8209608284582388</v>
+        <v>0.8827325790548115</v>
       </c>
       <c r="AL2">
-        <v>0.8999999761577999</v>
+        <v>0.8576380260848928</v>
       </c>
       <c r="AM2">
-        <v>146.6553654464649</v>
+        <v>-0.6164514392171101</v>
       </c>
       <c r="AN2">
-        <v>32.47568898723157</v>
+        <v>-117.37883833194</v>
       </c>
       <c r="AO2">
-        <v>-90.00000000000878</v>
+        <v>117.1203644707401</v>
       </c>
       <c r="AP2">
-        <v>147.5713439924405</v>
+        <v>2.073642055958752</v>
       </c>
       <c r="AQ2">
-        <v>35.28843500952931</v>
+        <v>-115.9946037575568</v>
       </c>
       <c r="AR2">
-        <v>-90.00000000000878</v>
+        <v>116.8149734530221</v>
       </c>
     </row>
   </sheetData>
@@ -4513,130 +4513,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0003580273367994191</v>
+        <v>0.0004134143585567791</v>
       </c>
       <c r="C2">
-        <v>0.000358027336799419</v>
+        <v>0.0002067071792783894</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.0002067071792783893</v>
       </c>
       <c r="E2">
-        <v>0.000358027336799419</v>
+        <v>0.0004134143585567792</v>
       </c>
       <c r="F2">
-        <v>0.0003580273367994192</v>
+        <v>0.0002067071792783895</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.0002067071792783895</v>
       </c>
       <c r="H2">
-        <v>0.004134143585567789</v>
+        <v>0.004773697823992257</v>
       </c>
       <c r="I2">
-        <v>0.004134143585567788</v>
+        <v>0.002386848911996127</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.002386848911996127</v>
       </c>
       <c r="K2">
-        <v>0.004134143585567788</v>
+        <v>0.004773697823992259</v>
       </c>
       <c r="L2">
-        <v>0.004134143585567789</v>
+        <v>0.002386848911996128</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.002386848911996128</v>
       </c>
       <c r="N2">
-        <v>0.003793080182498377</v>
+        <v>0.003205088038290295</v>
       </c>
       <c r="O2">
-        <v>0.001014551874937063</v>
+        <v>-0.0005879921442080829</v>
       </c>
       <c r="P2">
-        <v>2.339575494692676E-18</v>
+        <v>0.002190536163353231</v>
       </c>
       <c r="Q2">
-        <v>-0.003792952204015558</v>
+        <v>-0.003204917400313206</v>
       </c>
       <c r="R2">
-        <v>-0.001014423896454247</v>
+        <v>0.0005880348037023553</v>
       </c>
       <c r="S2">
-        <v>-2.569793325868187E-18</v>
+        <v>-0.002190493503858959</v>
       </c>
       <c r="T2">
-        <v>0.001018113988922676</v>
+        <v>0.003207955142679415</v>
       </c>
       <c r="U2">
-        <v>0.003793818725096436</v>
+        <v>0.002189841153756734</v>
       </c>
       <c r="V2">
-        <v>-2.5090665201412E-18</v>
+        <v>-0.0005858635824170283</v>
       </c>
       <c r="W2">
-        <v>-0.001018038360613619</v>
+        <v>-0.003207854304934006</v>
       </c>
       <c r="X2">
-        <v>-0.003793743096787381</v>
+        <v>-0.002189815944320383</v>
       </c>
       <c r="Y2">
-        <v>2.309340344240426E-18</v>
+        <v>0.0005858887918533815</v>
       </c>
       <c r="Z2">
+        <v>-45.02912710151706</v>
+      </c>
+      <c r="AA2">
         <v>134.9708728984757</v>
       </c>
-      <c r="AA2">
-        <v>-45.02912710151701</v>
-      </c>
       <c r="AB2">
-        <v>0</v>
+        <v>134.9708728984757</v>
       </c>
       <c r="AC2">
+        <v>134.9708728984756</v>
+      </c>
+      <c r="AD2">
+        <v>-45.029127101517</v>
+      </c>
+      <c r="AE2">
         <v>-45.02912710151703</v>
       </c>
-      <c r="AD2">
-        <v>134.9708728984757</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
       <c r="AG2">
-        <v>0.9499771082079528</v>
+        <v>0.9499358655887539</v>
       </c>
       <c r="AH2">
-        <v>0.949926684357142</v>
+        <v>0.949958746453205</v>
       </c>
       <c r="AI2">
-        <v>0.9499999880790705</v>
+        <v>0.9500091686022485</v>
       </c>
       <c r="AJ2">
-        <v>0.9499424676964709</v>
+        <v>0.9498956577715063</v>
       </c>
       <c r="AK2">
-        <v>0.9499010146965833</v>
+        <v>0.9499531809884819</v>
       </c>
       <c r="AL2">
-        <v>0.9499999880790705</v>
+        <v>0.9499946317120944</v>
       </c>
       <c r="AM2">
-        <v>149.9956916907817</v>
+        <v>-0.00351165416578378</v>
       </c>
       <c r="AN2">
-        <v>29.99904100574321</v>
+        <v>-119.999203177093</v>
       </c>
       <c r="AO2">
-        <v>-89.99999999999633</v>
+        <v>119.9974475277823</v>
       </c>
       <c r="AP2">
-        <v>149.9951100660698</v>
+        <v>-0.002886930252220094</v>
       </c>
       <c r="AQ2">
-        <v>30.00055977635476</v>
+        <v>-119.9979968766604</v>
       </c>
       <c r="AR2">
-        <v>-89.99999999999633</v>
+        <v>119.9965536493202</v>
       </c>
     </row>
   </sheetData>
@@ -4788,130 +4788,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0003391837880282381</v>
+        <v>0.0003916557026457207</v>
       </c>
       <c r="C2">
-        <v>0.0003391837880282379</v>
+        <v>0.0001958278513228602</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.0001958278513228602</v>
       </c>
       <c r="E2">
-        <v>0.0003391837880282381</v>
+        <v>0.0003916557026457206</v>
       </c>
       <c r="F2">
-        <v>0.000339183788028238</v>
+        <v>0.0001958278513228602</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.0001958278513228602</v>
       </c>
       <c r="H2">
-        <v>0.003916557026457205</v>
+        <v>0.004522450507043178</v>
       </c>
       <c r="I2">
-        <v>0.003916557026457203</v>
+        <v>0.002261225253521587</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.002261225253521587</v>
       </c>
       <c r="K2">
-        <v>0.003916557026457205</v>
+        <v>0.004522450507043177</v>
       </c>
       <c r="L2">
-        <v>0.003916557026457204</v>
+        <v>0.002261225253521587</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.002261225253521587</v>
       </c>
       <c r="N2">
-        <v>0.003404315636730521</v>
+        <v>0.002876588630051791</v>
       </c>
       <c r="O2">
-        <v>0.0009105673083471642</v>
+        <v>-0.0005277270066787314</v>
       </c>
       <c r="P2">
-        <v>1.753602915312749E-18</v>
+        <v>0.001966021321704627</v>
       </c>
       <c r="Q2">
-        <v>-0.003404200775159117</v>
+        <v>-0.002876435481289919</v>
       </c>
       <c r="R2">
-        <v>-0.0009104524467757609</v>
+        <v>0.0005277652938691998</v>
       </c>
       <c r="S2">
-        <v>-1.864265952554823E-18</v>
+        <v>-0.00196598303451416</v>
       </c>
       <c r="T2">
-        <v>0.0009137643302284799</v>
+        <v>0.002879161876024563</v>
       </c>
       <c r="U2">
-        <v>0.003404978483808356</v>
+        <v>0.00196539754579608</v>
       </c>
       <c r="V2">
-        <v>-1.893283144012266E-18</v>
+        <v>-0.0005258166077837987</v>
       </c>
       <c r="W2">
-        <v>-0.0009136964532992526</v>
+        <v>-0.00287907137345226</v>
       </c>
       <c r="X2">
-        <v>-0.003404910606879129</v>
+        <v>-0.001965374920153003</v>
       </c>
       <c r="Y2">
-        <v>2.48056032402421E-18</v>
+        <v>0.0005258392334268744</v>
       </c>
       <c r="Z2">
+        <v>-45.02912710151706</v>
+      </c>
+      <c r="AA2">
         <v>134.9708728984757</v>
       </c>
-      <c r="AA2">
-        <v>-45.02912710151699</v>
-      </c>
       <c r="AB2">
-        <v>0</v>
+        <v>134.9708728984757</v>
       </c>
       <c r="AC2">
-        <v>-45.02912710151702</v>
+        <v>134.9708728984756</v>
       </c>
       <c r="AD2">
-        <v>134.9708728984757</v>
+        <v>-45.02912710151703</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>-45.02912710151706</v>
       </c>
       <c r="AG2">
-        <v>0.8999783004910691</v>
+        <v>0.8999392285365833</v>
       </c>
       <c r="AH2">
-        <v>0.8999305305278091</v>
+        <v>0.8999609051447084</v>
       </c>
       <c r="AI2">
-        <v>0.8999999761581414</v>
+        <v>0.9000086734957679</v>
       </c>
       <c r="AJ2">
-        <v>0.8999454831648598</v>
+        <v>0.8999011369207747</v>
       </c>
       <c r="AK2">
-        <v>0.8999062119023556</v>
+        <v>0.899955632599255</v>
       </c>
       <c r="AL2">
-        <v>0.8999999761581414</v>
+        <v>0.8999949017052876</v>
       </c>
       <c r="AM2">
-        <v>149.9956916907817</v>
+        <v>-0.003511654165783781</v>
       </c>
       <c r="AN2">
-        <v>29.99904100574321</v>
+        <v>-119.999203177093</v>
       </c>
       <c r="AO2">
-        <v>-89.99999999999633</v>
+        <v>119.9974475277823</v>
       </c>
       <c r="AP2">
-        <v>149.9951100660698</v>
+        <v>-0.002886930252220097</v>
       </c>
       <c r="AQ2">
-        <v>30.00055977635475</v>
+        <v>-119.9979968766604</v>
       </c>
       <c r="AR2">
-        <v>-89.99999999999633</v>
+        <v>119.9965536493202</v>
       </c>
     </row>
   </sheetData>
@@ -5063,130 +5063,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.4836812079204414</v>
+        <v>0.3068982060771427</v>
       </c>
       <c r="C2">
-        <v>0.4776384146435675</v>
+        <v>0.7084147114474856</v>
       </c>
       <c r="D2">
-        <v>0.8010071194422387</v>
+        <v>0.7125029537814933</v>
       </c>
       <c r="E2">
-        <v>0.4836812079204411</v>
+        <v>0.3068982060771423</v>
       </c>
       <c r="F2">
-        <v>0.4776384146435674</v>
+        <v>0.7084147114474856</v>
       </c>
       <c r="G2">
-        <v>0.8010071194422385</v>
+        <v>0.7125029537814933</v>
       </c>
       <c r="H2">
-        <v>5.585069511896604</v>
+        <v>3.543755237849032</v>
       </c>
       <c r="I2">
-        <v>5.515293345395397</v>
+        <v>8.180068487041938</v>
       </c>
       <c r="J2">
-        <v>9.249233520655666</v>
+        <v>8.227275443282974</v>
       </c>
       <c r="K2">
-        <v>5.585069511896601</v>
+        <v>3.543755237849027</v>
       </c>
       <c r="L2">
-        <v>5.515293345395396</v>
+        <v>8.180068487041938</v>
       </c>
       <c r="M2">
-        <v>9.249233520655661</v>
+        <v>8.227275443282974</v>
       </c>
       <c r="N2">
-        <v>-1.998626103811125</v>
+        <v>0.3933041277701156</v>
       </c>
       <c r="O2">
-        <v>3.146336057880197</v>
+        <v>3.507437756403043</v>
       </c>
       <c r="P2">
-        <v>1.115507524821495</v>
+        <v>-1.637524405294612</v>
       </c>
       <c r="Q2">
-        <v>2.120278811986703</v>
+        <v>-0.3443271421350498</v>
       </c>
       <c r="R2">
-        <v>-3.027704058758064</v>
+        <v>-3.246475021253245</v>
       </c>
       <c r="S2">
-        <v>-0.7818690671312134</v>
+        <v>1.901507849497846</v>
       </c>
       <c r="T2">
-        <v>4.982254422420798</v>
+        <v>3.481581871823225</v>
       </c>
       <c r="U2">
-        <v>4.319143731542427</v>
+        <v>6.6573781418799</v>
       </c>
       <c r="V2">
-        <v>8.158050692470535</v>
+        <v>7.32048883275504</v>
       </c>
       <c r="W2">
-        <v>-4.844225390155863</v>
+        <v>-3.426011831239295</v>
       </c>
       <c r="X2">
-        <v>-4.184542042192038</v>
+        <v>-6.361285812081957</v>
       </c>
       <c r="Y2">
-        <v>-7.779499370991632</v>
+        <v>-7.020969160042566</v>
       </c>
       <c r="Z2">
-        <v>40.33541378483593</v>
+        <v>-83.77534760831865</v>
       </c>
       <c r="AA2">
-        <v>-26.80066687371135</v>
+        <v>174.4976046246248</v>
       </c>
       <c r="AB2">
-        <v>-172.9936292748583</v>
+        <v>19.44221106265062</v>
       </c>
       <c r="AC2">
-        <v>-139.6645862151568</v>
+        <v>96.22465239167401</v>
       </c>
       <c r="AD2">
-        <v>153.1993331262814</v>
+        <v>-5.502395375367949</v>
       </c>
       <c r="AE2">
-        <v>7.006370725134374</v>
+        <v>-160.5577889373421</v>
       </c>
       <c r="AG2">
-        <v>0.961166341690552</v>
+        <v>0.9887044727995762</v>
       </c>
       <c r="AH2">
-        <v>0.9688759041841465</v>
+        <v>0.9198960282307083</v>
       </c>
       <c r="AI2">
-        <v>0.890231938665311</v>
+        <v>0.9117724066042564</v>
       </c>
       <c r="AJ2">
-        <v>0.9467958029414922</v>
+        <v>0.9716448271876785</v>
       </c>
       <c r="AK2">
-        <v>0.9364896961419782</v>
+        <v>0.873075514507675</v>
       </c>
       <c r="AL2">
-        <v>0.845333943657895</v>
+        <v>0.8841211430118522</v>
       </c>
       <c r="AM2">
-        <v>152.1935505043372</v>
+        <v>-0.2205600447134146</v>
       </c>
       <c r="AN2">
-        <v>27.12738303722576</v>
+        <v>-123.2848863080102</v>
       </c>
       <c r="AO2">
-        <v>-90.77979689241764</v>
+        <v>122.0511655022732</v>
       </c>
       <c r="AP2">
-        <v>153.9740254310049</v>
+        <v>0.4854819550912287</v>
       </c>
       <c r="AQ2">
-        <v>27.31190617461291</v>
+        <v>-122.5398375441774</v>
       </c>
       <c r="AR2">
-        <v>-88.73279947482526</v>
+        <v>124.5962439009081</v>
       </c>
     </row>
   </sheetData>
@@ -5338,130 +5338,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.4870830479912519</v>
+        <v>0.3079432144546701</v>
       </c>
       <c r="C2">
-        <v>0.4812137823098317</v>
+        <v>0.71465044431016</v>
       </c>
       <c r="D2">
-        <v>0.8081745664549461</v>
+        <v>0.7186156475531219</v>
       </c>
       <c r="E2">
-        <v>0.4870830479912519</v>
+        <v>0.30794321445467</v>
       </c>
       <c r="F2">
-        <v>0.4812137823098314</v>
+        <v>0.7146504443101598</v>
       </c>
       <c r="G2">
-        <v>0.8081745664549459</v>
+        <v>0.7186156475531218</v>
       </c>
       <c r="H2">
-        <v>5.624350577509055</v>
+        <v>3.555821955210449</v>
       </c>
       <c r="I2">
-        <v>5.556578135086786</v>
+        <v>8.252072527979131</v>
       </c>
       <c r="J2">
-        <v>9.331996069899445</v>
+        <v>8.297858751173443</v>
       </c>
       <c r="K2">
-        <v>5.624350577509055</v>
+        <v>3.555821955210448</v>
       </c>
       <c r="L2">
-        <v>5.556578135086783</v>
+        <v>8.252072527979129</v>
       </c>
       <c r="M2">
-        <v>9.331996069899443</v>
+        <v>8.297858751173443</v>
       </c>
       <c r="N2">
-        <v>-2.12601034449715</v>
+        <v>0.4124955234422913</v>
       </c>
       <c r="O2">
-        <v>3.331484233554159</v>
+        <v>3.711967075713344</v>
       </c>
       <c r="P2">
-        <v>1.173461207776133</v>
+        <v>-1.745527502343147</v>
       </c>
       <c r="Q2">
-        <v>2.249380292775597</v>
+        <v>-0.3631844302939786</v>
       </c>
       <c r="R2">
-        <v>-3.211069544841549</v>
+        <v>-3.446389936306448</v>
       </c>
       <c r="S2">
-        <v>-0.8338252132390119</v>
+        <v>2.014059901315871</v>
       </c>
       <c r="T2">
-        <v>5.271637889579623</v>
+        <v>3.669588604957733</v>
       </c>
       <c r="U2">
-        <v>4.573651388680201</v>
+        <v>7.079763457043667</v>
       </c>
       <c r="V2">
-        <v>8.681812741657939</v>
+        <v>7.777749957937579</v>
       </c>
       <c r="W2">
-        <v>-5.131660450303289</v>
+        <v>-3.613639480854674</v>
       </c>
       <c r="X2">
-        <v>-4.43702703232394</v>
+        <v>-6.778435553261072</v>
       </c>
       <c r="Y2">
-        <v>-8.296456522701968</v>
+        <v>-7.473068971234923</v>
       </c>
       <c r="Z2">
-        <v>40.15321950517944</v>
+        <v>-83.79583750416985</v>
       </c>
       <c r="AA2">
-        <v>-26.69243734496884</v>
+        <v>174.5187426735358</v>
       </c>
       <c r="AB2">
-        <v>-173.0404130331558</v>
+        <v>19.33069449960511</v>
       </c>
       <c r="AC2">
-        <v>-139.8467804948132</v>
+        <v>96.20416249582293</v>
       </c>
       <c r="AD2">
-        <v>153.3075626550239</v>
+        <v>-5.481257326456906</v>
       </c>
       <c r="AE2">
-        <v>6.959586966836934</v>
+        <v>-160.6693055003876</v>
       </c>
       <c r="AG2">
-        <v>1.01064044373553</v>
+        <v>1.038494058183655</v>
       </c>
       <c r="AH2">
-        <v>1.018317941921281</v>
+        <v>0.9687090122595233</v>
       </c>
       <c r="AI2">
-        <v>0.9387871686725803</v>
+        <v>0.9606351160082519</v>
       </c>
       <c r="AJ2">
-        <v>0.9962045647949839</v>
+        <v>1.021379690676144</v>
       </c>
       <c r="AK2">
-        <v>0.9856892098029517</v>
+        <v>0.9214971657675533</v>
       </c>
       <c r="AL2">
-        <v>0.8935122209072558</v>
+        <v>0.9327364810675794</v>
       </c>
       <c r="AM2">
-        <v>152.1170545996768</v>
+        <v>-0.2094868086342073</v>
       </c>
       <c r="AN2">
-        <v>27.2376686426296</v>
+        <v>-123.1495789383115</v>
       </c>
       <c r="AO2">
-        <v>-90.73804141979615</v>
+        <v>121.9797583938115</v>
       </c>
       <c r="AP2">
-        <v>153.8226837647629</v>
+        <v>0.4649920594233971</v>
       </c>
       <c r="AQ2">
-        <v>27.41436187773105</v>
+        <v>-122.4316080138075</v>
       </c>
       <c r="AR2">
-        <v>-88.77958323313165</v>
+        <v>124.4140496211901</v>
       </c>
     </row>
   </sheetData>
@@ -5613,130 +5613,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0003957116525991963</v>
+        <v>0.0002284863193137288</v>
       </c>
       <c r="C2">
-        <v>0.0003957323761130154</v>
+        <v>0.0006044699684714056</v>
       </c>
       <c r="D2">
-        <v>0.0006853945262934872</v>
+        <v>0.0006044564014737175</v>
       </c>
       <c r="E2">
-        <v>0.0003957116525991961</v>
+        <v>0.0002284863193137287</v>
       </c>
       <c r="F2">
-        <v>0.0003957323761130151</v>
+        <v>0.0006044699684714053</v>
       </c>
       <c r="G2">
-        <v>0.0006853945262934872</v>
+        <v>0.0006044564014737175</v>
       </c>
       <c r="H2">
-        <v>0.004569284582992354</v>
+        <v>0.002638332759238562</v>
       </c>
       <c r="I2">
-        <v>0.004569523877517994</v>
+        <v>0.006979817980280212</v>
       </c>
       <c r="J2">
-        <v>0.007914254285132817</v>
+        <v>0.006979661322084867</v>
       </c>
       <c r="K2">
-        <v>0.004569284582992351</v>
+        <v>0.002638332759238562</v>
       </c>
       <c r="L2">
-        <v>0.004569523877517991</v>
+        <v>0.00697981798028021</v>
       </c>
       <c r="M2">
-        <v>0.007914254285132817</v>
+        <v>0.006979661322084867</v>
       </c>
       <c r="N2">
-        <v>0.001239549413946947</v>
+        <v>0.001957942871823441</v>
       </c>
       <c r="O2">
-        <v>0.004633808526421043</v>
+        <v>0.006591280723142141</v>
       </c>
       <c r="P2">
-        <v>0.005872887265265639</v>
+        <v>0.003197021610668045</v>
       </c>
       <c r="Q2">
-        <v>-0.001239467988335026</v>
+        <v>-0.001957915724703861</v>
       </c>
       <c r="R2">
-        <v>-0.004633727092280337</v>
+        <v>-0.006591090723487972</v>
       </c>
       <c r="S2">
-        <v>-0.00587264298711913</v>
+        <v>-0.003196831619542659</v>
       </c>
       <c r="T2">
-        <v>0.004634492030775583</v>
+        <v>0.001959654654488744</v>
       </c>
       <c r="U2">
-        <v>0.001244011736071743</v>
+        <v>0.003203206193941579</v>
       </c>
       <c r="V2">
-        <v>0.005878043570228421</v>
+        <v>0.006593686488645421</v>
       </c>
       <c r="W2">
-        <v>-0.004634399644024938</v>
+        <v>-0.001959623852949669</v>
       </c>
       <c r="X2">
-        <v>-0.001243919339644213</v>
+        <v>-0.00320299061741403</v>
       </c>
       <c r="Y2">
-        <v>-0.005877766408489301</v>
+        <v>-0.006593470921794756</v>
       </c>
       <c r="Z2">
-        <v>74.9730192768529</v>
+        <v>-45.02671465398004</v>
       </c>
       <c r="AA2">
-        <v>14.96835485909168</v>
+        <v>-145.9244496107951</v>
       </c>
       <c r="AB2">
-        <v>-135.0301791875454</v>
+        <v>55.86433874724727</v>
       </c>
       <c r="AC2">
-        <v>-105.0269807231398</v>
+        <v>134.9732853460127</v>
       </c>
       <c r="AD2">
-        <v>-165.031645140901</v>
+        <v>34.07555038919758</v>
       </c>
       <c r="AE2">
-        <v>44.96982081244737</v>
+        <v>-124.1356612527454</v>
       </c>
       <c r="AG2">
-        <v>1.049922575191129</v>
+        <v>1.049966131663271</v>
       </c>
       <c r="AH2">
-        <v>1.049975870953185</v>
+        <v>1.049942054488679</v>
       </c>
       <c r="AI2">
-        <v>1.049898497017663</v>
+        <v>1.04988875700999</v>
       </c>
       <c r="AJ2">
-        <v>1.049898438365347</v>
+        <v>1.049950600258694</v>
       </c>
       <c r="AK2">
-        <v>1.049953416632931</v>
+        <v>1.049904071386117</v>
       </c>
       <c r="AL2">
-        <v>1.049851907180983</v>
+        <v>1.049849090534432</v>
       </c>
       <c r="AM2">
-        <v>149.9990792468876</v>
+        <v>-0.001679433986690346</v>
       </c>
       <c r="AN2">
-        <v>29.99588285531672</v>
+        <v>-120.0057963455972</v>
       </c>
       <c r="AO2">
-        <v>-90.00503781811661</v>
+        <v>119.9974000636828</v>
       </c>
       <c r="AP2">
-        <v>149.9997336223455</v>
+        <v>-0.001732511182813301</v>
       </c>
       <c r="AQ2">
-        <v>29.99506933261959</v>
+        <v>-120.0066629985307</v>
       </c>
       <c r="AR2">
-        <v>-90.00519704499433</v>
+        <v>119.9980014197076</v>
       </c>
     </row>
   </sheetData>
@@ -5888,130 +5888,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0004145445592723857</v>
+        <v>0.0002393605538121244</v>
       </c>
       <c r="C2">
-        <v>0.0004145662678180388</v>
+        <v>0.0006332382039998826</v>
       </c>
       <c r="D2">
-        <v>0.0007180141641402953</v>
+        <v>0.0006332239921345021</v>
       </c>
       <c r="E2">
-        <v>0.0004145445592723854</v>
+        <v>0.0002393605538121244</v>
       </c>
       <c r="F2">
-        <v>0.0004145662678180387</v>
+        <v>0.0006332382039998821</v>
       </c>
       <c r="G2">
-        <v>0.0007180141641402947</v>
+        <v>0.0006332239921345021</v>
       </c>
       <c r="H2">
-        <v>0.004786748257740133</v>
+        <v>0.002763897603536159</v>
       </c>
       <c r="I2">
-        <v>0.004786998926433664</v>
+        <v>0.007312004950809747</v>
       </c>
       <c r="J2">
-        <v>0.008290913418967273</v>
+        <v>0.007311840846323686</v>
       </c>
       <c r="K2">
-        <v>0.004786748257740131</v>
+        <v>0.002763897603536159</v>
       </c>
       <c r="L2">
-        <v>0.004786998926433662</v>
+        <v>0.007312004950809742</v>
       </c>
       <c r="M2">
-        <v>0.008290913418967266</v>
+        <v>0.007311840846323686</v>
       </c>
       <c r="N2">
-        <v>0.00136027259081522</v>
+        <v>0.002148754457072164</v>
       </c>
       <c r="O2">
-        <v>0.005085474242490582</v>
+        <v>0.007233712161652032</v>
       </c>
       <c r="P2">
-        <v>0.006445230295395084</v>
+        <v>0.003508510509976671</v>
       </c>
       <c r="Q2">
-        <v>-0.001360183230273733</v>
+        <v>-0.002148724664464695</v>
       </c>
       <c r="R2">
-        <v>-0.005085384872589721</v>
+        <v>-0.007233503646523766</v>
       </c>
       <c r="S2">
-        <v>-0.006444962212332792</v>
+        <v>-0.003508302004207778</v>
       </c>
       <c r="T2">
-        <v>0.005086280955908347</v>
+        <v>0.002150722318949849</v>
       </c>
       <c r="U2">
-        <v>0.00136538093747673</v>
+        <v>0.003515598192962112</v>
       </c>
       <c r="V2">
-        <v>0.006451156829920614</v>
+        <v>0.007236498211393732</v>
       </c>
       <c r="W2">
-        <v>-0.005086179566064671</v>
+        <v>-0.002150688515799558</v>
       </c>
       <c r="X2">
-        <v>-0.001365279537013773</v>
+        <v>-0.003515361608493101</v>
       </c>
       <c r="Y2">
-        <v>-0.006450852658758224</v>
+        <v>-0.007236261637544011</v>
       </c>
       <c r="Z2">
-        <v>74.97183053822837</v>
+        <v>-45.02790351429179</v>
       </c>
       <c r="AA2">
-        <v>14.96716617676102</v>
+        <v>-145.9256382663911</v>
       </c>
       <c r="AB2">
-        <v>-135.0313678480669</v>
+        <v>55.86315006752626</v>
       </c>
       <c r="AC2">
-        <v>-105.0281694617643</v>
+        <v>134.9720964857009</v>
       </c>
       <c r="AD2">
-        <v>-165.0328338232317</v>
+        <v>34.07436173360161</v>
       </c>
       <c r="AE2">
-        <v>44.96863215192577</v>
+        <v>-124.1368499324664</v>
       </c>
       <c r="AG2">
-        <v>1.099918963779171</v>
+        <v>1.099964592910502</v>
       </c>
       <c r="AH2">
-        <v>1.099974794746676</v>
+        <v>1.099939368203312</v>
       </c>
       <c r="AI2">
-        <v>1.099893738025533</v>
+        <v>1.099883535437527</v>
       </c>
       <c r="AJ2">
-        <v>1.099893678482171</v>
+        <v>1.099948322306457</v>
       </c>
       <c r="AK2">
-        <v>1.099951271445219</v>
+        <v>1.099899577044821</v>
       </c>
       <c r="AL2">
-        <v>1.099844930798714</v>
+        <v>1.099841981374808</v>
       </c>
       <c r="AM2">
-        <v>149.9990793578895</v>
+        <v>-0.001679353016203436</v>
       </c>
       <c r="AN2">
-        <v>29.99588298720121</v>
+        <v>-120.0057961327618</v>
       </c>
       <c r="AO2">
-        <v>-90.00503757523742</v>
+        <v>119.9974002556425</v>
       </c>
       <c r="AP2">
-        <v>149.9997337440498</v>
+        <v>-0.001732411276575632</v>
       </c>
       <c r="AQ2">
-        <v>29.99506951059992</v>
+        <v>-120.0066627206637</v>
       </c>
       <c r="AR2">
-        <v>-90.00519674530969</v>
+        <v>119.9980016413038</v>
       </c>
     </row>
   </sheetData>
@@ -6163,130 +6163,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.4194713145387732</v>
+        <v>0.2642618041507926</v>
       </c>
       <c r="C2">
-        <v>0.4075464753715204</v>
+        <v>0.6070221088484327</v>
       </c>
       <c r="D2">
-        <v>0.6889105335371034</v>
+        <v>0.6150917775128535</v>
       </c>
       <c r="E2">
-        <v>0.4194713145387732</v>
+        <v>0.2642618041507926</v>
       </c>
       <c r="F2">
-        <v>0.4075464753715203</v>
+        <v>0.6070221088484328</v>
       </c>
       <c r="G2">
-        <v>0.6889105335371033</v>
+        <v>0.6150917775128538</v>
       </c>
       <c r="H2">
-        <v>4.843637527325738</v>
+        <v>3.051432475259925</v>
       </c>
       <c r="I2">
-        <v>4.70594134526061</v>
+        <v>7.009287558953939</v>
       </c>
       <c r="J2">
-        <v>7.954853639704307</v>
+        <v>7.102468066467428</v>
       </c>
       <c r="K2">
-        <v>4.843637527325738</v>
+        <v>3.051432475259926</v>
       </c>
       <c r="L2">
-        <v>4.70594134526061</v>
+        <v>7.00928755895394</v>
       </c>
       <c r="M2">
-        <v>7.954853639704306</v>
+        <v>7.102468066467432</v>
       </c>
       <c r="N2">
-        <v>-1.465687229206087</v>
+        <v>0.3378862801462812</v>
       </c>
       <c r="O2">
-        <v>2.513178359193272</v>
+        <v>2.884896928886187</v>
       </c>
       <c r="P2">
-        <v>1.081323419533782</v>
+        <v>-1.093968659515243</v>
       </c>
       <c r="Q2">
-        <v>1.641361886657608</v>
+        <v>-0.2681637124565197</v>
       </c>
       <c r="R2">
-        <v>-2.347349976791429</v>
+        <v>-2.51701064201003</v>
       </c>
       <c r="S2">
-        <v>-0.6074850428961296</v>
+        <v>1.471701221441069</v>
       </c>
       <c r="T2">
-        <v>3.943371191329645</v>
+        <v>2.70939750703492</v>
       </c>
       <c r="U2">
-        <v>3.282931475127782</v>
+        <v>5.090439127521263</v>
       </c>
       <c r="V2">
-        <v>6.32441281181432</v>
+        <v>5.750878843722038</v>
       </c>
       <c r="W2">
-        <v>-3.839557042305055</v>
+        <v>-2.668195269116682</v>
       </c>
       <c r="X2">
-        <v>-3.18493593807701</v>
+        <v>-4.87303838023132</v>
       </c>
       <c r="Y2">
-        <v>-6.044400153418187</v>
+        <v>-5.527659484458288</v>
       </c>
       <c r="Z2">
-        <v>41.69255037235193</v>
+        <v>-83.14615064896294</v>
       </c>
       <c r="AA2">
-        <v>-25.49787173129715</v>
+        <v>176.080112287559</v>
       </c>
       <c r="AB2">
-        <v>-171.3538824675234</v>
+        <v>21.04462284466868</v>
       </c>
       <c r="AC2">
-        <v>-138.3074496276408</v>
+        <v>96.85384935102975</v>
       </c>
       <c r="AD2">
-        <v>154.5021282686955</v>
+        <v>-3.919887712433635</v>
       </c>
       <c r="AE2">
-        <v>8.646117532469267</v>
+        <v>-158.955377155324</v>
       </c>
       <c r="AG2">
-        <v>0.8685514643818987</v>
+        <v>0.8947879314869135</v>
       </c>
       <c r="AH2">
-        <v>0.8785603241857284</v>
+        <v>0.83476179121788</v>
       </c>
       <c r="AI2">
-        <v>0.8065751372455499</v>
+        <v>0.8242212391851742</v>
       </c>
       <c r="AJ2">
-        <v>0.8620949906460225</v>
+        <v>0.8788125464043383</v>
       </c>
       <c r="AK2">
-        <v>0.8407450819515017</v>
+        <v>0.7824892172501785</v>
       </c>
       <c r="AL2">
-        <v>0.7636659323894043</v>
+        <v>0.8053849111972595</v>
       </c>
       <c r="AM2">
-        <v>152.0818356803778</v>
+        <v>-0.254750397886062</v>
       </c>
       <c r="AN2">
-        <v>27.06703434632475</v>
+        <v>-123.4613515559453</v>
       </c>
       <c r="AO2">
-        <v>-91.05627438104251</v>
+        <v>121.8151061382788</v>
       </c>
       <c r="AP2">
-        <v>154.8386431601303</v>
+        <v>1.114678914993751</v>
       </c>
       <c r="AQ2">
-        <v>28.11130518318954</v>
+        <v>-121.2370424077723</v>
       </c>
       <c r="AR2">
-        <v>-87.09305266722066</v>
+        <v>125.9533804819714</v>
       </c>
     </row>
   </sheetData>
@@ -6357,10 +6357,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0006853945262934878</v>
+        <v>0.0006853945262934887</v>
       </c>
       <c r="C2">
-        <v>0.0006853945262934878</v>
+        <v>0.0006853945262934887</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -6369,40 +6369,40 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.02374276285539847</v>
+        <v>0.0237427628553985</v>
       </c>
       <c r="G2">
-        <v>0.02374276285539847</v>
+        <v>0.0237427628553985</v>
       </c>
       <c r="H2">
-        <v>0.01761866179579698</v>
+        <v>0.01761866179579696</v>
       </c>
       <c r="I2">
-        <v>-0.01761792896135745</v>
+        <v>-0.01761792896135743</v>
       </c>
       <c r="J2">
-        <v>0.01763413071068521</v>
+        <v>0.0176341307106853</v>
       </c>
       <c r="K2">
-        <v>-0.01763329922546786</v>
+        <v>-0.01763329922546795</v>
       </c>
       <c r="L2">
-        <v>104.9698208124451</v>
+        <v>-45.03017918754901</v>
       </c>
       <c r="M2">
-        <v>-75.03017918754762</v>
+        <v>134.9698208124437</v>
       </c>
       <c r="N2">
-        <v>1.049898497017662</v>
+        <v>1.049898497017663</v>
       </c>
       <c r="O2">
-        <v>1.049851907180982</v>
+        <v>1.049851907180983</v>
       </c>
       <c r="P2">
-        <v>149.9949621818736</v>
+        <v>-0.005037818120266376</v>
       </c>
       <c r="Q2">
-        <v>149.9948029549959</v>
+        <v>-0.005197044997986872</v>
       </c>
     </row>
   </sheetData>
@@ -6554,130 +6554,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.3973938713907624</v>
+        <v>0.2503532846522785</v>
       </c>
       <c r="C2">
-        <v>0.386096655495089</v>
+        <v>0.5750735687857531</v>
       </c>
       <c r="D2">
-        <v>0.6526520753038997</v>
+        <v>0.5827185179401932</v>
       </c>
       <c r="E2">
-        <v>0.3973938713907624</v>
+        <v>0.2503532846522785</v>
       </c>
       <c r="F2">
-        <v>0.3860966554950889</v>
+        <v>0.5750735687857533</v>
       </c>
       <c r="G2">
-        <v>0.6526520753038997</v>
+        <v>0.5827185179401934</v>
       </c>
       <c r="H2">
-        <v>4.588709172435284</v>
+        <v>2.89083072573</v>
       </c>
       <c r="I2">
-        <v>4.458260159666077</v>
+        <v>6.640377594845868</v>
       </c>
       <c r="J2">
-        <v>7.536177027277488</v>
+        <v>6.728653863891007</v>
       </c>
       <c r="K2">
-        <v>4.588709172435284</v>
+        <v>2.89083072573</v>
       </c>
       <c r="L2">
-        <v>4.458260159666075</v>
+        <v>6.640377594845869</v>
       </c>
       <c r="M2">
-        <v>7.536177027277488</v>
+        <v>6.728653863891008</v>
       </c>
       <c r="N2">
-        <v>-1.31546440171902</v>
+        <v>0.3032552679076337</v>
       </c>
       <c r="O2">
-        <v>2.255594918760485</v>
+        <v>2.589214899985126</v>
       </c>
       <c r="P2">
-        <v>0.9704952303584329</v>
+        <v>-0.981844420496231</v>
       </c>
       <c r="Q2">
-        <v>1.47313361896862</v>
+        <v>-0.240678782307765</v>
       </c>
       <c r="R2">
-        <v>-2.106762801309047</v>
+        <v>-2.259034419031964</v>
       </c>
       <c r="S2">
-        <v>-0.5452220177557783</v>
+        <v>1.320862001247551</v>
       </c>
       <c r="T2">
-        <v>3.539202854191682</v>
+        <v>2.431702957895911</v>
       </c>
       <c r="U2">
-        <v>2.946453651747207</v>
+        <v>4.568704241899561</v>
       </c>
       <c r="V2">
-        <v>5.676204138193835</v>
+        <v>5.161453444343065</v>
       </c>
       <c r="W2">
-        <v>-3.446028939105739</v>
+        <v>-2.394723665061411</v>
       </c>
       <c r="X2">
-        <v>-2.858501981057236</v>
+        <v>-4.373585571102422</v>
       </c>
       <c r="Y2">
-        <v>-5.424890845145396</v>
+        <v>-4.96111252914996</v>
       </c>
       <c r="Z2">
-        <v>41.69255037235195</v>
+        <v>-83.14615064896302</v>
       </c>
       <c r="AA2">
-        <v>-25.49787173129709</v>
+        <v>176.0801122875591</v>
       </c>
       <c r="AB2">
-        <v>-171.3538824675234</v>
+        <v>21.0446228446687</v>
       </c>
       <c r="AC2">
-        <v>-138.3074496276408</v>
+        <v>96.85384935102968</v>
       </c>
       <c r="AD2">
-        <v>154.5021282686957</v>
+        <v>-3.919887712433611</v>
       </c>
       <c r="AE2">
-        <v>8.646117532469303</v>
+        <v>-158.955377155324</v>
       </c>
       <c r="AG2">
-        <v>0.8228382179419202</v>
+        <v>0.8476938180106454</v>
       </c>
       <c r="AH2">
-        <v>0.8323202955186064</v>
+        <v>0.7908269490749599</v>
       </c>
       <c r="AI2">
-        <v>0.7641238035787479</v>
+        <v>0.7808411630779402</v>
       </c>
       <c r="AJ2">
-        <v>0.8167215586984775</v>
+        <v>0.8325592428802738</v>
       </c>
       <c r="AK2">
-        <v>0.7964953296909376</v>
+        <v>0.7413055639012789</v>
       </c>
       <c r="AL2">
-        <v>0.7234729784923359</v>
+        <v>0.7629962210224051</v>
       </c>
       <c r="AM2">
-        <v>152.0818356803778</v>
+        <v>-0.2547503978860596</v>
       </c>
       <c r="AN2">
-        <v>27.06703434632474</v>
+        <v>-123.4613515559453</v>
       </c>
       <c r="AO2">
-        <v>-91.05627438104251</v>
+        <v>121.8151061382788</v>
       </c>
       <c r="AP2">
-        <v>154.8386431601303</v>
+        <v>1.114678914993756</v>
       </c>
       <c r="AQ2">
-        <v>28.11130518318953</v>
+        <v>-121.2370424077723</v>
       </c>
       <c r="AR2">
-        <v>-87.09305266722068</v>
+        <v>125.9533804819714</v>
       </c>
     </row>
   </sheetData>
@@ -6829,130 +6829,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0003580096974236677</v>
+        <v>0.0002067185303998365</v>
       </c>
       <c r="C2">
-        <v>0.0003580253189932197</v>
+        <v>0.0005468730199127065</v>
       </c>
       <c r="D2">
-        <v>0.0006200874878169703</v>
+        <v>0.0005468627929541678</v>
       </c>
       <c r="E2">
-        <v>0.0003580096974236678</v>
+        <v>0.0002067185303998366</v>
       </c>
       <c r="F2">
-        <v>0.0003580253189932195</v>
+        <v>0.0005468730199127062</v>
       </c>
       <c r="G2">
-        <v>0.0006200874878169703</v>
+        <v>0.000546862792954168</v>
       </c>
       <c r="H2">
-        <v>0.004133939903601021</v>
+        <v>0.00238697998345659</v>
       </c>
       <c r="I2">
-        <v>0.004134120285948741</v>
+        <v>0.006314745705182894</v>
       </c>
       <c r="J2">
-        <v>0.007160153560244931</v>
+        <v>0.006314627614437588</v>
       </c>
       <c r="K2">
-        <v>0.004133939903601022</v>
+        <v>0.00238697998345659</v>
       </c>
       <c r="L2">
-        <v>0.004134120285948738</v>
+        <v>0.00631474570518289</v>
       </c>
       <c r="M2">
-        <v>0.007160153560244931</v>
+        <v>0.00631462761443759</v>
       </c>
       <c r="N2">
-        <v>0.001014634540706328</v>
+        <v>0.001602677364060005</v>
       </c>
       <c r="O2">
-        <v>0.003792997543112145</v>
+        <v>0.005395274898810613</v>
       </c>
       <c r="P2">
-        <v>0.004807232075456935</v>
+        <v>0.002616911896404803</v>
       </c>
       <c r="Q2">
-        <v>-0.001014506574833748</v>
+        <v>-0.001602634699880397</v>
       </c>
       <c r="R2">
-        <v>-0.003792869566071868</v>
+        <v>-0.005394976307216702</v>
       </c>
       <c r="S2">
-        <v>-0.004806848182170054</v>
+        <v>-0.002616613315978589</v>
       </c>
       <c r="T2">
-        <v>0.00379359635185666</v>
+        <v>0.001604128525684833</v>
       </c>
       <c r="U2">
-        <v>0.001018336394330901</v>
+        <v>0.002622012089148789</v>
       </c>
       <c r="V2">
-        <v>0.004811479915320617</v>
+        <v>0.005397272046674552</v>
       </c>
       <c r="W2">
-        <v>-0.003793520730999569</v>
+        <v>-0.001604103313479701</v>
       </c>
       <c r="X2">
-        <v>-0.001018260766874308</v>
+        <v>-0.002621835637788771</v>
       </c>
       <c r="Y2">
-        <v>-0.004811253055308641</v>
+        <v>-0.005397095601914037</v>
       </c>
       <c r="Z2">
-        <v>74.9728761801309</v>
+        <v>-45.02768371578634</v>
       </c>
       <c r="AA2">
-        <v>14.9674267066325</v>
+        <v>-145.9250296287295</v>
       </c>
       <c r="AB2">
-        <v>-135.0305703287363</v>
+        <v>55.86409520156384</v>
       </c>
       <c r="AC2">
-        <v>-105.0271238198618</v>
+        <v>134.9723162842064</v>
       </c>
       <c r="AD2">
-        <v>-165.0325732933602</v>
+        <v>34.07497037126318</v>
       </c>
       <c r="AE2">
-        <v>44.96942967125644</v>
+        <v>-124.1359047984288</v>
       </c>
       <c r="AG2">
-        <v>0.9499266885246511</v>
+        <v>0.9499679253606668</v>
       </c>
       <c r="AH2">
-        <v>0.9499771040403568</v>
+        <v>0.9499450465922316</v>
       </c>
       <c r="AI2">
-        <v>0.9499038087630122</v>
+        <v>0.9498946293750816</v>
       </c>
       <c r="AJ2">
-        <v>0.9499010192483888</v>
+        <v>0.949947820362174</v>
       </c>
       <c r="AK2">
-        <v>0.9499424631441235</v>
+        <v>0.9498903042541738</v>
       </c>
       <c r="AL2">
-        <v>0.9498435003064293</v>
+        <v>0.9498488580826374</v>
       </c>
       <c r="AM2">
-        <v>149.9990408984097</v>
+        <v>-0.001755912959688212</v>
       </c>
       <c r="AN2">
-        <v>29.99569179806639</v>
+        <v>-120.0060638671884</v>
       </c>
       <c r="AO2">
-        <v>-90.00526722363965</v>
+        <v>119.9972852529967</v>
       </c>
       <c r="AP2">
-        <v>150.0005595400493</v>
+        <v>-0.001443544392112483</v>
       </c>
       <c r="AQ2">
-        <v>29.99511030230262</v>
+        <v>-120.0063331224146</v>
       </c>
       <c r="AR2">
-        <v>-90.00433015760088</v>
+        <v>119.9991163515854</v>
       </c>
     </row>
   </sheetData>
@@ -7104,130 +7104,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.000339167077040917</v>
+        <v>0.0001958386050167128</v>
       </c>
       <c r="C2">
-        <v>0.0003391818764223913</v>
+        <v>0.0005180902221674565</v>
       </c>
       <c r="D2">
-        <v>0.0005874512960570529</v>
+        <v>0.0005180805334700284</v>
       </c>
       <c r="E2">
-        <v>0.0003391670770409171</v>
+        <v>0.0001958386050167128</v>
       </c>
       <c r="F2">
-        <v>0.0003391818764223913</v>
+        <v>0.0005180902221674565</v>
       </c>
       <c r="G2">
-        <v>0.0005874512960570529</v>
+        <v>0.0005180805334700284</v>
       </c>
       <c r="H2">
-        <v>0.00391636406459664</v>
+        <v>0.002261349426482399</v>
       </c>
       <c r="I2">
-        <v>0.0039165349531342</v>
+        <v>0.005982390584657881</v>
       </c>
       <c r="J2">
-        <v>0.006783303278286682</v>
+        <v>0.005982278709216517</v>
       </c>
       <c r="K2">
-        <v>0.003916364064596641</v>
+        <v>0.002261349426482399</v>
       </c>
       <c r="L2">
-        <v>0.0039165349531342</v>
+        <v>0.005982390584657881</v>
       </c>
       <c r="M2">
-        <v>0.006783303278286682</v>
+        <v>0.005982278709216517</v>
       </c>
       <c r="N2">
-        <v>0.0009106415014454866</v>
+        <v>0.001438413993007084</v>
       </c>
       <c r="O2">
-        <v>0.003404241467311147</v>
+        <v>0.004842296450053625</v>
       </c>
       <c r="P2">
-        <v>0.004314523958492025</v>
+        <v>0.002348696484187967</v>
       </c>
       <c r="Q2">
-        <v>-0.0009105266511918594</v>
+        <v>-0.001438375701611494</v>
       </c>
       <c r="R2">
-        <v>-0.003404126607034436</v>
+        <v>-0.004842028462037755</v>
       </c>
       <c r="S2">
-        <v>-0.004314179411618115</v>
+        <v>-0.002348428506195179</v>
       </c>
       <c r="T2">
-        <v>0.003404778902291241</v>
+        <v>0.001439716420578644</v>
       </c>
       <c r="U2">
-        <v>0.0009139639406169997</v>
+        <v>0.002353273942367944</v>
       </c>
       <c r="V2">
-        <v>0.00431833642408054</v>
+        <v>0.004844088904042188</v>
       </c>
       <c r="W2">
-        <v>-0.003404711032050204</v>
+        <v>-0.00143969379245057</v>
       </c>
       <c r="X2">
-        <v>-0.0009138960644528628</v>
+        <v>-0.002353115576054784</v>
       </c>
       <c r="Y2">
-        <v>-0.004318132815654417</v>
+        <v>-0.004843930543652124</v>
       </c>
       <c r="Z2">
-        <v>74.9728761801309</v>
+        <v>-45.02768371578633</v>
       </c>
       <c r="AA2">
-        <v>14.96742670663247</v>
+        <v>-145.9250296287295</v>
       </c>
       <c r="AB2">
-        <v>-135.0305703287362</v>
+        <v>55.86409520156386</v>
       </c>
       <c r="AC2">
-        <v>-105.0271238198618</v>
+        <v>134.9723162842064</v>
       </c>
       <c r="AD2">
-        <v>-165.0325732933602</v>
+        <v>34.07497037126318</v>
       </c>
       <c r="AE2">
-        <v>44.96942967125644</v>
+        <v>-124.1359047984289</v>
       </c>
       <c r="AG2">
-        <v>0.8999305344759757</v>
+        <v>0.8999696009516562</v>
       </c>
       <c r="AH2">
-        <v>0.8999782965428202</v>
+        <v>0.8999479263292304</v>
       </c>
       <c r="AI2">
-        <v>0.8999088589126198</v>
+        <v>0.8999001626504911</v>
       </c>
       <c r="AJ2">
-        <v>0.8999062162145924</v>
+        <v>0.8999505541112444</v>
       </c>
       <c r="AK2">
-        <v>0.8999454788521094</v>
+        <v>0.8998960651675829</v>
       </c>
       <c r="AL2">
-        <v>0.8998517245861274</v>
+        <v>0.8998568003740433</v>
       </c>
       <c r="AM2">
-        <v>149.9990408984097</v>
+        <v>-0.001755912959688214</v>
       </c>
       <c r="AN2">
-        <v>29.99569179806639</v>
+        <v>-120.0060638671884</v>
       </c>
       <c r="AO2">
-        <v>-90.00526722363966</v>
+        <v>119.9972852529967</v>
       </c>
       <c r="AP2">
-        <v>150.0005595400493</v>
+        <v>-0.001443544392112483</v>
       </c>
       <c r="AQ2">
-        <v>29.99511030230261</v>
+        <v>-120.0063331224146</v>
       </c>
       <c r="AR2">
-        <v>-90.00433015760088</v>
+        <v>119.9991163515854</v>
       </c>
     </row>
   </sheetData>
@@ -7298,10 +7298,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0007180141641402959</v>
+        <v>0.0007180141641402971</v>
       </c>
       <c r="C2">
-        <v>0.0007180141641402959</v>
+        <v>0.0007180141641402971</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7310,40 +7310,40 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.02487274025690183</v>
+        <v>0.02487274025690188</v>
       </c>
       <c r="G2">
-        <v>0.02487274025690183</v>
+        <v>0.02487274025690188</v>
       </c>
       <c r="H2">
-        <v>0.01933569088618532</v>
+        <v>0.01933569088618537</v>
       </c>
       <c r="I2">
-        <v>-0.01933488663699847</v>
+        <v>-0.01933488663699852</v>
       </c>
       <c r="J2">
-        <v>0.01935347048976177</v>
+        <v>0.01935347048976183</v>
       </c>
       <c r="K2">
-        <v>-0.01935255797627461</v>
+        <v>-0.01935255797627466</v>
       </c>
       <c r="L2">
-        <v>104.9686321519235</v>
+        <v>-45.03136784807036</v>
       </c>
       <c r="M2">
-        <v>-75.03136784806915</v>
+        <v>134.9686321519223</v>
       </c>
       <c r="N2">
-        <v>1.099893738025532</v>
+        <v>1.099893738025533</v>
       </c>
       <c r="O2">
-        <v>1.099844930798714</v>
+        <v>1.099844930798715</v>
       </c>
       <c r="P2">
-        <v>149.9949624247528</v>
+        <v>-0.005037575241080463</v>
       </c>
       <c r="Q2">
-        <v>149.9948032546806</v>
+        <v>-0.005196745313343392</v>
       </c>
     </row>
   </sheetData>
@@ -7414,10 +7414,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.6889105335360737</v>
+        <v>0.6889105335368642</v>
       </c>
       <c r="C2">
-        <v>0.6889105335360737</v>
+        <v>0.6889105335368642</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7426,40 +7426,40 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>23.86456091907725</v>
+        <v>23.86456091910463</v>
       </c>
       <c r="G2">
-        <v>23.86456091907725</v>
+        <v>23.86456091910463</v>
       </c>
       <c r="H2">
-        <v>3.243970258588271</v>
+        <v>3.243970258585431</v>
       </c>
       <c r="I2">
-        <v>-1.822455128679608</v>
+        <v>-1.822455128673494</v>
       </c>
       <c r="J2">
-        <v>18.97323843540899</v>
+        <v>18.97323843541324</v>
       </c>
       <c r="K2">
-        <v>-18.13320046022309</v>
+        <v>-18.13320046022536</v>
       </c>
       <c r="L2">
-        <v>68.64611753243254</v>
+        <v>-81.35388246757607</v>
       </c>
       <c r="M2">
-        <v>-111.3538824675602</v>
+        <v>98.64611753241664</v>
       </c>
       <c r="N2">
-        <v>0.8065751372452601</v>
+        <v>0.8065751372444899</v>
       </c>
       <c r="O2">
-        <v>0.7636659323891967</v>
+        <v>0.7636659323883896</v>
       </c>
       <c r="P2">
-        <v>148.9437256189348</v>
+        <v>-1.056274381063374</v>
       </c>
       <c r="Q2">
-        <v>152.9069473327529</v>
+        <v>2.906947332764127</v>
       </c>
     </row>
   </sheetData>
@@ -7530,10 +7530,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.652652075302924</v>
+        <v>0.6526520753036738</v>
       </c>
       <c r="C2">
-        <v>0.652652075302924</v>
+        <v>0.6526520753036738</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7542,40 +7542,40 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>22.60853108179866</v>
+        <v>22.60853108182463</v>
       </c>
       <c r="G2">
-        <v>22.60853108179866</v>
+        <v>22.60853108182463</v>
       </c>
       <c r="H2">
-        <v>2.91148569106356</v>
+        <v>2.911485691061023</v>
       </c>
       <c r="I2">
-        <v>-1.635666053259438</v>
+        <v>-1.635666053253959</v>
       </c>
       <c r="J2">
-        <v>17.02861241455102</v>
+        <v>17.02861241455485</v>
       </c>
       <c r="K2">
-        <v>-16.27467253540794</v>
+        <v>-16.27467253541</v>
       </c>
       <c r="L2">
-        <v>68.64611753243253</v>
+        <v>-81.35388246757606</v>
       </c>
       <c r="M2">
-        <v>-111.3538824675602</v>
+        <v>98.64611753241665</v>
       </c>
       <c r="N2">
-        <v>0.7641238035784736</v>
+        <v>0.764123803577744</v>
       </c>
       <c r="O2">
-        <v>0.7234729784921393</v>
+        <v>0.7234729784913747</v>
       </c>
       <c r="P2">
-        <v>148.9437256189348</v>
+        <v>-1.056274381063374</v>
       </c>
       <c r="Q2">
-        <v>152.9069473327529</v>
+        <v>2.906947332764126</v>
       </c>
     </row>
   </sheetData>
@@ -7646,10 +7646,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0006200874878169694</v>
+        <v>0.0006200874878169702</v>
       </c>
       <c r="C2">
-        <v>0.0006200874878169694</v>
+        <v>0.0006200874878169702</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7658,40 +7658,40 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.02148046068073476</v>
+        <v>0.02148046068073479</v>
       </c>
       <c r="G2">
-        <v>0.02148046068073476</v>
+        <v>0.02148046068073479</v>
       </c>
       <c r="H2">
-        <v>0.01442169622637076</v>
+        <v>0.01442169622637078</v>
       </c>
       <c r="I2">
-        <v>-0.01442054454651012</v>
+        <v>-0.01442054454651014</v>
       </c>
       <c r="J2">
-        <v>0.0144344397459618</v>
+        <v>0.01443443974596179</v>
       </c>
       <c r="K2">
-        <v>-0.01443375916592587</v>
+        <v>-0.01443375916592586</v>
       </c>
       <c r="L2">
-        <v>104.969429671254</v>
+        <v>-45.03057032873991</v>
       </c>
       <c r="M2">
-        <v>-75.03057032873875</v>
+        <v>134.9694296712528</v>
       </c>
       <c r="N2">
-        <v>0.9499038087630102</v>
+        <v>0.9499038087630096</v>
       </c>
       <c r="O2">
-        <v>0.9498435003064272</v>
+        <v>0.9498435003064266</v>
       </c>
       <c r="P2">
-        <v>149.9947327763505</v>
+        <v>-0.005267223643389589</v>
       </c>
       <c r="Q2">
-        <v>149.9956698423893</v>
+        <v>-0.004330157604604896</v>
       </c>
     </row>
   </sheetData>
@@ -7762,10 +7762,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0005874512960570526</v>
+        <v>0.000587451296057053</v>
       </c>
       <c r="C2">
-        <v>0.0005874512960570526</v>
+        <v>0.000587451296057053</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7774,13 +7774,13 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.02034990983486003</v>
+        <v>0.02034990983486005</v>
       </c>
       <c r="G2">
-        <v>0.02034990983486003</v>
+        <v>0.02034990983486005</v>
       </c>
       <c r="H2">
-        <v>0.01294357187547605</v>
+        <v>0.01294357187547606</v>
       </c>
       <c r="I2">
         <v>-0.01294253823485433</v>
@@ -7792,22 +7792,22 @@
         <v>-0.01295439844696319</v>
       </c>
       <c r="L2">
-        <v>104.969429671254</v>
+        <v>-45.0305703287399</v>
       </c>
       <c r="M2">
-        <v>-75.03057032873869</v>
+        <v>134.9694296712528</v>
       </c>
       <c r="N2">
-        <v>0.8999088589126178</v>
+        <v>0.8999088589126175</v>
       </c>
       <c r="O2">
-        <v>0.8998517245861254</v>
+        <v>0.8998517245861249</v>
       </c>
       <c r="P2">
-        <v>149.9947327763505</v>
+        <v>-0.00526722364338959</v>
       </c>
       <c r="Q2">
-        <v>149.9956698423893</v>
+        <v>-0.004330157604604898</v>
       </c>
     </row>
   </sheetData>
@@ -7956,130 +7956,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.4005035597209305</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4005035597209318</v>
+        <v>0.693692514049176</v>
       </c>
       <c r="D2">
-        <v>0.8010071194418623</v>
+        <v>0.6936925140491751</v>
       </c>
       <c r="E2">
-        <v>0.4005035597209305</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.4005035597209315</v>
+        <v>0.6936925140491755</v>
       </c>
       <c r="G2">
-        <v>0.8010071194418624</v>
+        <v>0.693692514049175</v>
       </c>
       <c r="H2">
-        <v>4.624616760325652</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>4.624616760325667</v>
+        <v>8.010071194422402</v>
       </c>
       <c r="J2">
-        <v>9.24923352065132</v>
+        <v>8.010071194422391</v>
       </c>
       <c r="K2">
-        <v>4.624616760325652</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>4.624616760325663</v>
+        <v>8.010071194422396</v>
       </c>
       <c r="M2">
-        <v>9.249233520651321</v>
+        <v>8.010071194422389</v>
       </c>
       <c r="N2">
-        <v>-3.895007721637154</v>
+        <v>-1.243449731109643E-15</v>
       </c>
       <c r="O2">
-        <v>4.452761484047644</v>
+        <v>5.010515246465562</v>
       </c>
       <c r="P2">
-        <v>1.115507524820963</v>
+        <v>-3.337253959231207</v>
       </c>
       <c r="Q2">
-        <v>3.978417336059647</v>
+        <v>1.243449731109643E-15</v>
       </c>
       <c r="R2">
-        <v>-4.369351869625151</v>
+        <v>-4.760286403197853</v>
       </c>
       <c r="S2">
-        <v>-0.781869067130995</v>
+        <v>3.587482802498916</v>
       </c>
       <c r="T2">
-        <v>2.552472359257651</v>
+        <v>-3.108624327774126E-15</v>
       </c>
       <c r="U2">
-        <v>1.526552986973992</v>
+        <v>5.605578333214108</v>
       </c>
       <c r="V2">
-        <v>8.158050692463355</v>
+        <v>6.631497705499537</v>
       </c>
       <c r="W2">
-        <v>-2.457834528888016</v>
+        <v>3.108624327774125E-15</v>
       </c>
       <c r="X2">
-        <v>-1.431915156604352</v>
+        <v>-5.321664842104926</v>
       </c>
       <c r="Y2">
-        <v>-7.779499370984807</v>
+        <v>-6.347584214390359</v>
       </c>
       <c r="Z2">
-        <v>7.006370725123273</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>7.006370725123301</v>
+        <v>-172.9936292747915</v>
       </c>
       <c r="AB2">
-        <v>-172.9936292748694</v>
+        <v>7.006370725201151</v>
       </c>
       <c r="AC2">
-        <v>-172.9936292748694</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>-172.9936292748694</v>
+        <v>7.00637072520118</v>
       </c>
       <c r="AE2">
-        <v>7.006370725123283</v>
+        <v>-172.9936292747915</v>
       </c>
       <c r="AF2">
-        <v>1.00696872807238</v>
+        <v>1.04999995231488</v>
       </c>
       <c r="AG2">
-        <v>1.017850815582785</v>
+        <v>0.9386302707479496</v>
       </c>
       <c r="AH2">
-        <v>0.8902319386649522</v>
+        <v>0.9268184944731632</v>
       </c>
       <c r="AI2">
-        <v>1.011198185105096</v>
+        <v>1.04999995231488</v>
       </c>
       <c r="AJ2">
-        <v>0.9942448483038008</v>
+        <v>0.8913852178494904</v>
       </c>
       <c r="AK2">
-        <v>0.8453339436575555</v>
+        <v>0.9102563143322974</v>
       </c>
       <c r="AL2">
-        <v>153.7687858258752</v>
+        <v>1.093074158024795E-13</v>
       </c>
       <c r="AM2">
-        <v>25.92977054708546</v>
+        <v>-124.7853905097055</v>
       </c>
       <c r="AN2">
-        <v>-90.77979689243183</v>
+        <v>123.719871368878</v>
       </c>
       <c r="AO2">
-        <v>155.298928846517</v>
+        <v>1.086715853001715E-13</v>
       </c>
       <c r="AP2">
-        <v>25.15127081984923</v>
+        <v>-124.8066037900613</v>
       </c>
       <c r="AQ2">
-        <v>-88.73279947483975</v>
+        <v>126.4803292649318</v>
       </c>
     </row>
   </sheetData>
